--- a/DRAGO/Noviembre/EXPENSAS-Noviembre.xlsx
+++ b/DRAGO/Noviembre/EXPENSAS-Noviembre.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\DRAGO\Octubre\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\DRAGO\Noviembre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17B155AD-45A3-41BB-8F50-1D7A88208E7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33FFE254-7B9E-4E4C-A809-29D0DE189B20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="detalle y gastos" sheetId="3" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="93">
   <si>
     <t>UF</t>
   </si>
@@ -259,27 +259,12 @@
     <t>Mauro</t>
   </si>
   <si>
-    <t>Articulos de limpieza</t>
-  </si>
-  <si>
-    <t>LIQUIDACIÓN EXPENSAS OCTUBRE 2025</t>
-  </si>
-  <si>
-    <t>Período OCTUBRE 2025</t>
-  </si>
-  <si>
-    <t>Vto. 14/11</t>
-  </si>
-  <si>
     <t>Compra de bomba y colocacion en UF PA 1</t>
   </si>
   <si>
     <t>Gasto particular PA 1 - Arreglo bacha</t>
   </si>
   <si>
-    <t>Ferreteria V&amp;A - Compra de manguera</t>
-  </si>
-  <si>
     <t>Egresos extraordinarios</t>
   </si>
   <si>
@@ -308,6 +293,18 @@
   </si>
   <si>
     <t>LAS EXPENSAS SE TRANSFIEREN A UNA CUENTA DE MERCADO PAGO: ALIAS: carolina.canciani CVU: 0000003100080478547818</t>
+  </si>
+  <si>
+    <t>Vto. 15/12</t>
+  </si>
+  <si>
+    <t>LIQUIDACIÓN EXPENSAS NOVIEMBRE 2025</t>
+  </si>
+  <si>
+    <t>Período NOVIEMBRE 2025</t>
+  </si>
+  <si>
+    <t>Recarga de matafuegos-  Matafuegos FIRE</t>
   </si>
 </sst>
 </file>
@@ -847,7 +844,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="123">
+  <cellXfs count="125">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1014,42 +1011,42 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="18" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="25" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1065,6 +1062,8 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="4" fontId="16" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -1433,16 +1432,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:H58"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
-    <col min="2" max="2" width="40.28515625" customWidth="1"/>
-    <col min="3" max="3" width="16.42578125" customWidth="1"/>
-    <col min="4" max="4" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="40.33203125" customWidth="1"/>
+    <col min="3" max="3" width="16.44140625" customWidth="1"/>
+    <col min="4" max="4" width="12.109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
         <v>17</v>
       </c>
@@ -1450,43 +1449,43 @@
         <v>61</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B4" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3"/>
       <c r="B5" s="21"/>
       <c r="C5" s="3"/>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="22" t="s">
         <v>35</v>
       </c>
       <c r="B7" s="23" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="C7" s="23" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="3"/>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="13" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>37</v>
       </c>
@@ -1494,7 +1493,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>38</v>
       </c>
@@ -1502,37 +1501,37 @@
         <v>46</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" s="19" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" s="53" t="s">
         <v>12</v>
       </c>
       <c r="B16" s="46"/>
       <c r="C16" s="84"/>
     </row>
-    <row r="17" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="46" t="s">
         <v>49</v>
       </c>
       <c r="B17" s="54" t="s">
         <v>74</v>
       </c>
-      <c r="C17" s="51">
-        <v>41718</v>
+      <c r="C17" s="123">
+        <v>43870.01</v>
       </c>
       <c r="D17" s="5"/>
       <c r="E17" s="12"/>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" s="46" t="s">
         <v>62</v>
       </c>
@@ -1543,22 +1542,22 @@
       <c r="D18" s="38"/>
       <c r="E18" s="12"/>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" s="46" t="s">
         <v>42</v>
       </c>
       <c r="B19" s="56" t="s">
         <v>65</v>
       </c>
-      <c r="C19" s="51">
-        <v>16346.58</v>
+      <c r="C19" s="123">
+        <v>20706.509999999998</v>
       </c>
       <c r="D19" s="5"/>
       <c r="E19" s="12"/>
       <c r="F19" s="14"/>
       <c r="H19" s="86"/>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" s="46" t="s">
         <v>31</v>
       </c>
@@ -1572,7 +1571,7 @@
       <c r="F20" s="12"/>
       <c r="H20" s="86"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" s="46" t="s">
         <v>32</v>
       </c>
@@ -1585,30 +1584,30 @@
       <c r="D21" s="5"/>
       <c r="E21" s="12"/>
       <c r="H21" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" s="57"/>
       <c r="B22" s="58"/>
       <c r="C22" s="42">
         <f>SUM(C17:C21)</f>
-        <v>284845.88</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+        <v>291357.82</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" s="53" t="s">
         <v>33</v>
       </c>
       <c r="B23" s="56"/>
       <c r="C23" s="84"/>
     </row>
-    <row r="24" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A24" s="46" t="s">
         <v>63</v>
       </c>
       <c r="B24" s="59" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="C24" s="51">
         <f>68460+68460*5%</f>
@@ -1616,9 +1615,9 @@
       </c>
       <c r="F24" s="18"/>
     </row>
-    <row r="25" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A25" s="46" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="B25" s="59"/>
       <c r="C25" s="51">
@@ -1626,25 +1625,25 @@
       </c>
       <c r="F25" s="18"/>
     </row>
-    <row r="26" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A26" s="46" t="s">
-        <v>83</v>
-      </c>
+    <row r="26" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A26" s="124"/>
       <c r="B26" s="59"/>
-      <c r="C26" s="51">
-        <v>15000</v>
+      <c r="C26" s="123">
+        <v>180000</v>
       </c>
       <c r="F26" s="18"/>
     </row>
-    <row r="27" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A27" s="46" t="s">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="B27" s="59"/>
-      <c r="C27" s="51"/>
+      <c r="C27" s="123">
+        <v>60899.97</v>
+      </c>
       <c r="F27" s="18"/>
     </row>
-    <row r="28" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A28" s="46" t="s">
         <v>69</v>
       </c>
@@ -1654,40 +1653,40 @@
       <c r="E28" s="12"/>
       <c r="F28" s="18"/>
     </row>
-    <row r="29" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A29" s="57"/>
       <c r="B29" s="58"/>
       <c r="C29" s="42">
         <f>SUM(C23:C28)</f>
-        <v>147782.97</v>
+        <v>373682.93999999994</v>
       </c>
       <c r="F29" s="18"/>
     </row>
-    <row r="30" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A30" s="49" t="s">
         <v>68</v>
       </c>
       <c r="B30" s="49"/>
       <c r="C30" s="60">
         <f>+C29+C22</f>
-        <v>432628.85</v>
+        <v>665040.76</v>
       </c>
       <c r="F30" s="18"/>
     </row>
-    <row r="31" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C31" s="43"/>
       <c r="F31" s="18"/>
     </row>
-    <row r="32" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A32" s="19" t="s">
         <v>43</v>
       </c>
       <c r="C32" s="43"/>
       <c r="F32" s="18"/>
     </row>
-    <row r="33" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A33" s="104" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="B33" s="105"/>
       <c r="C33" s="101">
@@ -1696,23 +1695,23 @@
       </c>
       <c r="F33" s="18"/>
     </row>
-    <row r="34" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A34" s="46"/>
       <c r="B34" s="46"/>
       <c r="C34" s="52"/>
       <c r="F34" s="18"/>
     </row>
-    <row r="35" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A35" s="46"/>
       <c r="B35" s="46"/>
       <c r="C35" s="52"/>
       <c r="F35" s="18"/>
     </row>
-    <row r="36" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C36" s="44"/>
       <c r="F36" s="18"/>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" s="19" t="s">
         <v>39</v>
       </c>
@@ -1723,22 +1722,22 @@
       </c>
       <c r="E37" s="12"/>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" s="29" t="s">
         <v>14</v>
       </c>
       <c r="B39" s="29"/>
       <c r="C39" s="30">
         <f>+C37+C30</f>
-        <v>540628.85</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+        <v>773040.76</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" s="5" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" s="31" t="s">
         <v>9</v>
       </c>
@@ -1749,7 +1748,7 @@
       <c r="D42" s="6"/>
       <c r="E42" s="6"/>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>8</v>
       </c>
@@ -1760,7 +1759,7 @@
       <c r="D43" s="12"/>
       <c r="E43" s="12"/>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>67</v>
       </c>
@@ -1768,9 +1767,9 @@
       <c r="D44" s="12"/>
       <c r="E44" s="12"/>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C45" s="61">
         <v>-20000</v>
@@ -1778,9 +1777,9 @@
       <c r="D45" s="12"/>
       <c r="E45" s="12"/>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="C46" s="61">
         <f>-C37</f>
@@ -1789,43 +1788,43 @@
       <c r="D46" s="12"/>
       <c r="E46" s="12"/>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>66</v>
       </c>
       <c r="C47" s="61">
         <f>-(C30-C28)</f>
-        <v>-432628.85</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+        <v>-665040.76</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48" s="31" t="s">
         <v>15</v>
       </c>
       <c r="B48" s="28"/>
       <c r="C48" s="33">
         <f>SUM(C42:C47)</f>
-        <v>66868.53562338918</v>
+        <v>-165543.37437661085</v>
       </c>
       <c r="D48" s="6"/>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49" s="15"/>
       <c r="B49" s="14"/>
       <c r="C49" s="16"/>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50" s="15"/>
       <c r="B50" s="14"/>
       <c r="C50" s="16"/>
       <c r="F50" s="62"/>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51" s="15"/>
       <c r="B51" s="14"/>
       <c r="C51" s="16"/>
     </row>
-    <row r="52" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A52" s="45" t="s">
         <v>60</v>
       </c>
@@ -1834,12 +1833,12 @@
         <v>109834.99657000002</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A53" s="46"/>
       <c r="B53" s="46"/>
       <c r="C53" s="50"/>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A54" s="49" t="s">
         <v>4</v>
       </c>
@@ -1849,22 +1848,22 @@
         <v>109834.99657000002</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A55" s="14"/>
       <c r="B55" s="14"/>
       <c r="C55" s="14"/>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A56" s="14"/>
       <c r="B56" s="14"/>
       <c r="C56" s="14"/>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A57" s="14"/>
       <c r="B57" s="14"/>
       <c r="C57" s="14"/>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A58" s="14"/>
       <c r="B58" s="14"/>
       <c r="C58" s="14"/>
@@ -1889,24 +1888,24 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Q39"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5.28515625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="5.33203125" style="1" customWidth="1"/>
     <col min="2" max="2" width="8" style="1" customWidth="1"/>
-    <col min="3" max="3" width="23.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.28515625" customWidth="1"/>
-    <col min="6" max="6" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.42578125" customWidth="1"/>
-    <col min="8" max="8" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.42578125" customWidth="1"/>
-    <col min="10" max="10" width="9.140625" customWidth="1"/>
-    <col min="11" max="12" width="12.42578125" customWidth="1"/>
-    <col min="13" max="13" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11.42578125" style="17"/>
+    <col min="3" max="3" width="23.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.33203125" customWidth="1"/>
+    <col min="6" max="6" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.44140625" customWidth="1"/>
+    <col min="8" max="8" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.44140625" customWidth="1"/>
+    <col min="10" max="10" width="9.109375" customWidth="1"/>
+    <col min="11" max="12" width="12.44140625" customWidth="1"/>
+    <col min="13" max="13" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.44140625" style="17"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="40" t="s">
         <v>47</v>
       </c>
@@ -1915,13 +1914,13 @@
       </c>
       <c r="G1" t="str">
         <f>'detalle y gastos'!C7</f>
-        <v>Vto. 14/11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+        <v>Vto. 15/12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2" s="71" t="str">
         <f>'detalle y gastos'!B7</f>
-        <v>LIQUIDACIÓN EXPENSAS OCTUBRE 2025</v>
+        <v>LIQUIDACIÓN EXPENSAS NOVIEMBRE 2025</v>
       </c>
       <c r="B2" s="66"/>
       <c r="C2" s="72"/>
@@ -1938,61 +1937,61 @@
       <c r="L2" s="66"/>
       <c r="M2" s="67"/>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A3" s="109"/>
-      <c r="B3" s="107" t="s">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A3" s="116"/>
+      <c r="B3" s="113" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="115" t="s">
+      <c r="C3" s="110" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="116" t="s">
+      <c r="D3" s="111" t="s">
         <v>54</v>
       </c>
-      <c r="E3" s="107" t="s">
+      <c r="E3" s="113" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="113" t="s">
+      <c r="F3" s="108" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="115" t="s">
+      <c r="G3" s="110" t="s">
         <v>52</v>
       </c>
-      <c r="H3" s="113" t="s">
+      <c r="H3" s="108" t="s">
         <v>44</v>
       </c>
-      <c r="I3" s="115" t="s">
+      <c r="I3" s="110" t="s">
         <v>6</v>
       </c>
-      <c r="J3" s="117" t="s">
-        <v>92</v>
-      </c>
-      <c r="K3" s="111" t="s">
+      <c r="J3" s="112" t="s">
+        <v>87</v>
+      </c>
+      <c r="K3" s="106" t="s">
         <v>70</v>
       </c>
-      <c r="L3" s="111" t="s">
+      <c r="L3" s="106" t="s">
         <v>71</v>
       </c>
-      <c r="M3" s="111" t="s">
+      <c r="M3" s="106" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A4" s="110"/>
-      <c r="B4" s="108"/>
-      <c r="C4" s="115"/>
-      <c r="D4" s="116"/>
-      <c r="E4" s="108"/>
-      <c r="F4" s="114"/>
-      <c r="G4" s="115"/>
-      <c r="H4" s="114"/>
-      <c r="I4" s="115"/>
-      <c r="J4" s="117"/>
-      <c r="K4" s="112"/>
-      <c r="L4" s="112"/>
-      <c r="M4" s="112"/>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A4" s="117"/>
+      <c r="B4" s="114"/>
+      <c r="C4" s="110"/>
+      <c r="D4" s="111"/>
+      <c r="E4" s="114"/>
+      <c r="F4" s="109"/>
+      <c r="G4" s="110"/>
+      <c r="H4" s="109"/>
+      <c r="I4" s="110"/>
+      <c r="J4" s="112"/>
+      <c r="K4" s="107"/>
+      <c r="L4" s="107"/>
+      <c r="M4" s="107"/>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A5" s="68">
         <v>1</v>
       </c>
@@ -2036,7 +2035,7 @@
         <v>54439.547406399994</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A6" s="68">
         <v>2</v>
       </c>
@@ -2083,7 +2082,7 @@
       <c r="O6" s="83"/>
       <c r="Q6" s="82"/>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A7" s="68">
         <v>3</v>
       </c>
@@ -2128,7 +2127,7 @@
         <v>52642.278467999997</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A8" s="68">
         <v>4</v>
       </c>
@@ -2173,7 +2172,7 @@
         <v>52642.278467999997</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A9" s="68">
         <v>5</v>
       </c>
@@ -2218,7 +2217,7 @@
         <v>61640.958548000002</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A10" s="68">
         <v>6</v>
       </c>
@@ -2229,7 +2228,7 @@
         <v>26</v>
       </c>
       <c r="D10" s="41" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="E10" s="37">
         <v>99619.343603999994</v>
@@ -2262,7 +2261,7 @@
         <v>186903.52939660478</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A11" s="68">
         <v>7</v>
       </c>
@@ -2307,7 +2306,7 @@
         <v>57141.618508</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A12" s="68">
         <v>8</v>
       </c>
@@ -2352,7 +2351,7 @@
         <v>57141.618508</v>
       </c>
     </row>
-    <row r="13" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="77" t="s">
         <v>10</v>
       </c>
@@ -2393,339 +2392,344 @@
         <v>577443.77779100474</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="C15" s="106" t="s">
-        <v>93</v>
-      </c>
-      <c r="D15" s="106"/>
-      <c r="E15" s="106"/>
-      <c r="F15" s="106"/>
-      <c r="G15" s="106"/>
-      <c r="H15" s="106"/>
-      <c r="I15" s="106"/>
-      <c r="J15" s="106"/>
-      <c r="K15" s="106"/>
-      <c r="L15" s="106"/>
-    </row>
-    <row r="16" spans="1:17" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="C15" s="115" t="s">
+        <v>88</v>
+      </c>
+      <c r="D15" s="115"/>
+      <c r="E15" s="115"/>
+      <c r="F15" s="115"/>
+      <c r="G15" s="115"/>
+      <c r="H15" s="115"/>
+      <c r="I15" s="115"/>
+      <c r="J15" s="115"/>
+      <c r="K15" s="115"/>
+      <c r="L15" s="115"/>
+    </row>
+    <row r="16" spans="1:17" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="40" t="s">
         <v>48</v>
       </c>
-      <c r="C16" s="106"/>
-      <c r="D16" s="106"/>
-      <c r="E16" s="106"/>
-      <c r="F16" s="106"/>
-      <c r="G16" s="106"/>
-      <c r="H16" s="106"/>
-      <c r="I16" s="106"/>
-      <c r="J16" s="106"/>
-      <c r="K16" s="106"/>
-      <c r="L16" s="106"/>
-    </row>
-    <row r="17" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C16" s="115"/>
+      <c r="D16" s="115"/>
+      <c r="E16" s="115"/>
+      <c r="F16" s="115"/>
+      <c r="G16" s="115"/>
+      <c r="H16" s="115"/>
+      <c r="I16" s="115"/>
+      <c r="J16" s="115"/>
+      <c r="K16" s="115"/>
+      <c r="L16" s="115"/>
+    </row>
+    <row r="17" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="24" t="s">
         <v>50</v>
       </c>
       <c r="B17" s="25"/>
-      <c r="C17" s="106"/>
-      <c r="D17" s="106"/>
-      <c r="E17" s="106"/>
-      <c r="F17" s="106"/>
-      <c r="G17" s="106"/>
-      <c r="H17" s="106"/>
-      <c r="I17" s="106"/>
-      <c r="J17" s="106"/>
-      <c r="K17" s="106"/>
-      <c r="L17" s="106"/>
+      <c r="C17" s="115"/>
+      <c r="D17" s="115"/>
+      <c r="E17" s="115"/>
+      <c r="F17" s="115"/>
+      <c r="G17" s="115"/>
+      <c r="H17" s="115"/>
+      <c r="I17" s="115"/>
+      <c r="J17" s="115"/>
+      <c r="K17" s="115"/>
+      <c r="L17" s="115"/>
       <c r="M17" s="26"/>
     </row>
-    <row r="18" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B18" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C18" s="106"/>
-      <c r="D18" s="106"/>
-      <c r="E18" s="106"/>
-      <c r="F18" s="106"/>
-      <c r="G18" s="106"/>
-      <c r="H18" s="106"/>
-      <c r="I18" s="106"/>
-      <c r="J18" s="106"/>
-      <c r="K18" s="106"/>
-      <c r="L18" s="106"/>
+      <c r="C18" s="115"/>
+      <c r="D18" s="115"/>
+      <c r="E18" s="115"/>
+      <c r="F18" s="115"/>
+      <c r="G18" s="115"/>
+      <c r="H18" s="115"/>
+      <c r="I18" s="115"/>
+      <c r="J18" s="115"/>
+      <c r="K18" s="115"/>
+      <c r="L18" s="115"/>
       <c r="M18" s="36" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="2"/>
       <c r="B19" s="7"/>
-      <c r="C19" s="106"/>
-      <c r="D19" s="106"/>
-      <c r="E19" s="106"/>
-      <c r="F19" s="106"/>
-      <c r="G19" s="106"/>
-      <c r="H19" s="106"/>
-      <c r="I19" s="106"/>
-      <c r="J19" s="106"/>
-      <c r="K19" s="106"/>
-      <c r="L19" s="106"/>
+      <c r="C19" s="115"/>
+      <c r="D19" s="115"/>
+      <c r="E19" s="115"/>
+      <c r="F19" s="115"/>
+      <c r="G19" s="115"/>
+      <c r="H19" s="115"/>
+      <c r="I19" s="115"/>
+      <c r="J19" s="115"/>
+      <c r="K19" s="115"/>
+      <c r="L19" s="115"/>
       <c r="M19" s="32" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="10">
         <v>1</v>
       </c>
       <c r="B20" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="C20" s="106"/>
-      <c r="D20" s="106"/>
-      <c r="E20" s="106"/>
-      <c r="F20" s="106"/>
-      <c r="G20" s="106"/>
-      <c r="H20" s="106"/>
-      <c r="I20" s="106"/>
-      <c r="J20" s="106"/>
-      <c r="K20" s="106"/>
-      <c r="L20" s="106"/>
+      <c r="C20" s="115"/>
+      <c r="D20" s="115"/>
+      <c r="E20" s="115"/>
+      <c r="F20" s="115"/>
+      <c r="G20" s="115"/>
+      <c r="H20" s="115"/>
+      <c r="I20" s="115"/>
+      <c r="J20" s="115"/>
+      <c r="K20" s="115"/>
+      <c r="L20" s="115"/>
       <c r="M20" s="34" t="e">
         <f>+#REF!+H20+K20</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="21" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="10">
         <v>2</v>
       </c>
       <c r="B21" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="C21" s="106"/>
-      <c r="D21" s="106"/>
-      <c r="E21" s="106"/>
-      <c r="F21" s="106"/>
-      <c r="G21" s="106"/>
-      <c r="H21" s="106"/>
-      <c r="I21" s="106"/>
-      <c r="J21" s="106"/>
-      <c r="K21" s="106"/>
-      <c r="L21" s="106"/>
+      <c r="C21" s="115"/>
+      <c r="D21" s="115"/>
+      <c r="E21" s="115"/>
+      <c r="F21" s="115"/>
+      <c r="G21" s="115"/>
+      <c r="H21" s="115"/>
+      <c r="I21" s="115"/>
+      <c r="J21" s="115"/>
+      <c r="K21" s="115"/>
+      <c r="L21" s="115"/>
       <c r="M21" s="34" t="e">
         <f>+#REF!+H21+K21</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="22" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="10">
         <v>3</v>
       </c>
       <c r="B22" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="C22" s="106"/>
-      <c r="D22" s="106"/>
-      <c r="E22" s="106"/>
-      <c r="F22" s="106"/>
-      <c r="G22" s="106"/>
-      <c r="H22" s="106"/>
-      <c r="I22" s="106"/>
-      <c r="J22" s="106"/>
-      <c r="K22" s="106"/>
-      <c r="L22" s="106"/>
+      <c r="C22" s="115"/>
+      <c r="D22" s="115"/>
+      <c r="E22" s="115"/>
+      <c r="F22" s="115"/>
+      <c r="G22" s="115"/>
+      <c r="H22" s="115"/>
+      <c r="I22" s="115"/>
+      <c r="J22" s="115"/>
+      <c r="K22" s="115"/>
+      <c r="L22" s="115"/>
       <c r="M22" s="34" t="e">
         <f>+#REF!+H22+K22</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="23" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="10">
         <v>4</v>
       </c>
       <c r="B23" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="C23" s="106"/>
-      <c r="D23" s="106"/>
-      <c r="E23" s="106"/>
-      <c r="F23" s="106"/>
-      <c r="G23" s="106"/>
-      <c r="H23" s="106"/>
-      <c r="I23" s="106"/>
-      <c r="J23" s="106"/>
-      <c r="K23" s="106"/>
-      <c r="L23" s="106"/>
+      <c r="C23" s="115"/>
+      <c r="D23" s="115"/>
+      <c r="E23" s="115"/>
+      <c r="F23" s="115"/>
+      <c r="G23" s="115"/>
+      <c r="H23" s="115"/>
+      <c r="I23" s="115"/>
+      <c r="J23" s="115"/>
+      <c r="K23" s="115"/>
+      <c r="L23" s="115"/>
       <c r="M23" s="34" t="e">
         <f>+#REF!+H23+K23</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="24" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="10">
         <v>5</v>
       </c>
       <c r="B24" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="C24" s="106"/>
-      <c r="D24" s="106"/>
-      <c r="E24" s="106"/>
-      <c r="F24" s="106"/>
-      <c r="G24" s="106"/>
-      <c r="H24" s="106"/>
-      <c r="I24" s="106"/>
-      <c r="J24" s="106"/>
-      <c r="K24" s="106"/>
-      <c r="L24" s="106"/>
+      <c r="C24" s="115"/>
+      <c r="D24" s="115"/>
+      <c r="E24" s="115"/>
+      <c r="F24" s="115"/>
+      <c r="G24" s="115"/>
+      <c r="H24" s="115"/>
+      <c r="I24" s="115"/>
+      <c r="J24" s="115"/>
+      <c r="K24" s="115"/>
+      <c r="L24" s="115"/>
       <c r="M24" s="34" t="e">
         <f>+#REF!+H24+K24</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="25" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="10">
         <v>6</v>
       </c>
       <c r="B25" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="C25" s="106"/>
-      <c r="D25" s="106"/>
-      <c r="E25" s="106"/>
-      <c r="F25" s="106"/>
-      <c r="G25" s="106"/>
-      <c r="H25" s="106"/>
-      <c r="I25" s="106"/>
-      <c r="J25" s="106"/>
-      <c r="K25" s="106"/>
-      <c r="L25" s="106"/>
+      <c r="C25" s="115"/>
+      <c r="D25" s="115"/>
+      <c r="E25" s="115"/>
+      <c r="F25" s="115"/>
+      <c r="G25" s="115"/>
+      <c r="H25" s="115"/>
+      <c r="I25" s="115"/>
+      <c r="J25" s="115"/>
+      <c r="K25" s="115"/>
+      <c r="L25" s="115"/>
       <c r="M25" s="34" t="e">
         <f>+#REF!+H25+K25</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="26" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="10">
         <v>7</v>
       </c>
       <c r="B26" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="C26" s="106"/>
-      <c r="D26" s="106"/>
-      <c r="E26" s="106"/>
-      <c r="F26" s="106"/>
-      <c r="G26" s="106"/>
-      <c r="H26" s="106"/>
-      <c r="I26" s="106"/>
-      <c r="J26" s="106"/>
-      <c r="K26" s="106"/>
-      <c r="L26" s="106"/>
+      <c r="C26" s="115"/>
+      <c r="D26" s="115"/>
+      <c r="E26" s="115"/>
+      <c r="F26" s="115"/>
+      <c r="G26" s="115"/>
+      <c r="H26" s="115"/>
+      <c r="I26" s="115"/>
+      <c r="J26" s="115"/>
+      <c r="K26" s="115"/>
+      <c r="L26" s="115"/>
       <c r="M26" s="34" t="e">
         <f>+#REF!+H26+K26</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="27" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="10">
         <v>8</v>
       </c>
       <c r="B27" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="C27" s="106"/>
-      <c r="D27" s="106"/>
-      <c r="E27" s="106"/>
-      <c r="F27" s="106"/>
-      <c r="G27" s="106"/>
-      <c r="H27" s="106"/>
-      <c r="I27" s="106"/>
-      <c r="J27" s="106"/>
-      <c r="K27" s="106"/>
-      <c r="L27" s="106"/>
+      <c r="C27" s="115"/>
+      <c r="D27" s="115"/>
+      <c r="E27" s="115"/>
+      <c r="F27" s="115"/>
+      <c r="G27" s="115"/>
+      <c r="H27" s="115"/>
+      <c r="I27" s="115"/>
+      <c r="J27" s="115"/>
+      <c r="K27" s="115"/>
+      <c r="L27" s="115"/>
       <c r="M27" s="34" t="e">
         <f>+#REF!+H27+K27</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="28" spans="1:13" ht="15.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:13" ht="15.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="8" t="s">
         <v>10</v>
       </c>
       <c r="B28" s="9"/>
-      <c r="C28" s="106"/>
-      <c r="D28" s="106"/>
-      <c r="E28" s="106"/>
-      <c r="F28" s="106"/>
-      <c r="G28" s="106"/>
-      <c r="H28" s="106"/>
-      <c r="I28" s="106"/>
-      <c r="J28" s="106"/>
-      <c r="K28" s="106"/>
-      <c r="L28" s="106"/>
+      <c r="C28" s="115"/>
+      <c r="D28" s="115"/>
+      <c r="E28" s="115"/>
+      <c r="F28" s="115"/>
+      <c r="G28" s="115"/>
+      <c r="H28" s="115"/>
+      <c r="I28" s="115"/>
+      <c r="J28" s="115"/>
+      <c r="K28" s="115"/>
+      <c r="L28" s="115"/>
       <c r="M28" s="35" t="e">
         <f>SUM(M20:M27)</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="C29" s="106"/>
-      <c r="D29" s="106"/>
-      <c r="E29" s="106"/>
-      <c r="F29" s="106"/>
-      <c r="G29" s="106"/>
-      <c r="H29" s="106"/>
-      <c r="I29" s="106"/>
-      <c r="J29" s="106"/>
-      <c r="K29" s="106"/>
-      <c r="L29" s="106"/>
-    </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="C30" s="106"/>
-      <c r="D30" s="106"/>
-      <c r="E30" s="106"/>
-      <c r="F30" s="106"/>
-      <c r="G30" s="106"/>
-      <c r="H30" s="106"/>
-      <c r="I30" s="106"/>
-      <c r="J30" s="106"/>
-      <c r="K30" s="106"/>
-      <c r="L30" s="106"/>
-    </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="C31" s="106"/>
-      <c r="D31" s="106"/>
-      <c r="E31" s="106"/>
-      <c r="F31" s="106"/>
-      <c r="G31" s="106"/>
-      <c r="H31" s="106"/>
-      <c r="I31" s="106"/>
-      <c r="J31" s="106"/>
-      <c r="K31" s="106"/>
-      <c r="L31" s="106"/>
-    </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="C32" s="106"/>
-      <c r="D32" s="106"/>
-      <c r="E32" s="106"/>
-      <c r="F32" s="106"/>
-      <c r="G32" s="106"/>
-      <c r="H32" s="106"/>
-      <c r="I32" s="106"/>
-      <c r="J32" s="106"/>
-      <c r="K32" s="106"/>
-      <c r="L32" s="106"/>
-    </row>
-    <row r="39" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="C29" s="115"/>
+      <c r="D29" s="115"/>
+      <c r="E29" s="115"/>
+      <c r="F29" s="115"/>
+      <c r="G29" s="115"/>
+      <c r="H29" s="115"/>
+      <c r="I29" s="115"/>
+      <c r="J29" s="115"/>
+      <c r="K29" s="115"/>
+      <c r="L29" s="115"/>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="C30" s="115"/>
+      <c r="D30" s="115"/>
+      <c r="E30" s="115"/>
+      <c r="F30" s="115"/>
+      <c r="G30" s="115"/>
+      <c r="H30" s="115"/>
+      <c r="I30" s="115"/>
+      <c r="J30" s="115"/>
+      <c r="K30" s="115"/>
+      <c r="L30" s="115"/>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="C31" s="115"/>
+      <c r="D31" s="115"/>
+      <c r="E31" s="115"/>
+      <c r="F31" s="115"/>
+      <c r="G31" s="115"/>
+      <c r="H31" s="115"/>
+      <c r="I31" s="115"/>
+      <c r="J31" s="115"/>
+      <c r="K31" s="115"/>
+      <c r="L31" s="115"/>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="C32" s="115"/>
+      <c r="D32" s="115"/>
+      <c r="E32" s="115"/>
+      <c r="F32" s="115"/>
+      <c r="G32" s="115"/>
+      <c r="H32" s="115"/>
+      <c r="I32" s="115"/>
+      <c r="J32" s="115"/>
+      <c r="K32" s="115"/>
+      <c r="L32" s="115"/>
+    </row>
+    <row r="39" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E39" s="39"/>
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="C15:L32"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="K3:K4"/>
+    <mergeCell ref="L3:L4"/>
     <mergeCell ref="M3:M4"/>
     <mergeCell ref="H3:H4"/>
     <mergeCell ref="F3:F4"/>
@@ -2735,11 +2739,6 @@
     <mergeCell ref="J3:J4"/>
     <mergeCell ref="I3:I4"/>
     <mergeCell ref="E3:E4"/>
-    <mergeCell ref="C15:L32"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="K3:K4"/>
-    <mergeCell ref="L3:L4"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -2750,20 +2749,20 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:L13"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.28515625" customWidth="1"/>
-    <col min="3" max="3" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.85546875" customWidth="1"/>
-    <col min="5" max="5" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="21.28515625" customWidth="1"/>
+    <col min="1" max="1" width="6.33203125" customWidth="1"/>
+    <col min="3" max="3" width="14.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.88671875" customWidth="1"/>
+    <col min="5" max="5" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="21.33203125" customWidth="1"/>
     <col min="7" max="7" width="18" customWidth="1"/>
-    <col min="8" max="8" width="8.140625" customWidth="1"/>
+    <col min="8" max="8" width="8.109375" customWidth="1"/>
     <col min="9" max="9" width="12" customWidth="1"/>
     <col min="10" max="10" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="91" t="s">
         <v>48</v>
       </c>
@@ -2780,9 +2779,9 @@
       <c r="J1" s="94"/>
       <c r="L1" s="17"/>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="95" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="B2" s="88"/>
       <c r="C2" s="89"/>
@@ -2799,53 +2798,53 @@
       <c r="J2" s="96"/>
       <c r="L2" s="17"/>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" s="119" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="107" t="s">
+      <c r="B3" s="113" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="107" t="s">
+      <c r="C3" s="113" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="116" t="s">
+      <c r="D3" s="111" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="115" t="s">
+      <c r="E3" s="110" t="s">
         <v>51</v>
       </c>
-      <c r="F3" s="116" t="s">
-        <v>88</v>
-      </c>
-      <c r="G3" s="116" t="s">
-        <v>90</v>
-      </c>
-      <c r="H3" s="115" t="s">
+      <c r="F3" s="111" t="s">
+        <v>83</v>
+      </c>
+      <c r="G3" s="111" t="s">
+        <v>85</v>
+      </c>
+      <c r="H3" s="110" t="s">
         <v>6</v>
       </c>
       <c r="I3" s="122" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="J3" s="121" t="s">
         <v>53</v>
       </c>
       <c r="L3" s="17"/>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" s="120"/>
-      <c r="B4" s="108"/>
-      <c r="C4" s="108"/>
-      <c r="D4" s="116"/>
-      <c r="E4" s="115"/>
-      <c r="F4" s="116"/>
-      <c r="G4" s="116"/>
-      <c r="H4" s="115"/>
+      <c r="B4" s="114"/>
+      <c r="C4" s="114"/>
+      <c r="D4" s="111"/>
+      <c r="E4" s="110"/>
+      <c r="F4" s="111"/>
+      <c r="G4" s="111"/>
+      <c r="H4" s="110"/>
       <c r="I4" s="122"/>
       <c r="J4" s="121"/>
       <c r="L4" s="17"/>
     </row>
-    <row r="5" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="98">
         <v>1</v>
       </c>
@@ -2881,7 +2880,7 @@
       </c>
       <c r="L5" s="17"/>
     </row>
-    <row r="6" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="98">
         <v>2</v>
       </c>
@@ -2917,7 +2916,7 @@
       </c>
       <c r="L6" s="17"/>
     </row>
-    <row r="7" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="98">
         <v>3</v>
       </c>
@@ -2953,7 +2952,7 @@
       </c>
       <c r="L7" s="17"/>
     </row>
-    <row r="8" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="98">
         <v>4</v>
       </c>
@@ -2989,7 +2988,7 @@
       </c>
       <c r="L8" s="17"/>
     </row>
-    <row r="9" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="98">
         <v>5</v>
       </c>
@@ -3025,7 +3024,7 @@
       </c>
       <c r="L9" s="17"/>
     </row>
-    <row r="10" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="98">
         <v>6</v>
       </c>
@@ -3061,7 +3060,7 @@
       </c>
       <c r="L10" s="17"/>
     </row>
-    <row r="11" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="98">
         <v>7</v>
       </c>
@@ -3097,7 +3096,7 @@
       </c>
       <c r="L11" s="17"/>
     </row>
-    <row r="12" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="98">
         <v>8</v>
       </c>
@@ -3133,7 +3132,7 @@
       </c>
       <c r="L12" s="17"/>
     </row>
-    <row r="13" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="77" t="s">
         <v>10</v>
       </c>

--- a/DRAGO/Noviembre/EXPENSAS-Noviembre.xlsx
+++ b/DRAGO/Noviembre/EXPENSAS-Noviembre.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\DRAGO\Noviembre\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\DRAGO\Noviembre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33FFE254-7B9E-4E4C-A809-29D0DE189B20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8111940-9741-4867-BB11-7629FE0943AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="detalle y gastos" sheetId="3" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="extraordinarias" sheetId="4" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'detalle y gastos'!$A$1:$C$49</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'detalle y gastos'!$A$1:$C$47</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'prorrateo '!$A$1:$M$33</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="89">
   <si>
     <t>UF</t>
   </si>
@@ -229,9 +229,6 @@
     <t>Egresos por gastos del mes ordinarios</t>
   </si>
   <si>
-    <t>Punitorios mal cobrados</t>
-  </si>
-  <si>
     <t xml:space="preserve">TOTAL GASTOS ORDINARIOS (A) </t>
   </si>
   <si>
@@ -253,39 +250,21 @@
     <t>Mercantil Andina</t>
   </si>
   <si>
-    <t>No llego factura</t>
-  </si>
-  <si>
     <t>Mauro</t>
   </si>
   <si>
-    <t>Compra de bomba y colocacion en UF PA 1</t>
-  </si>
-  <si>
-    <t>Gasto particular PA 1 - Arreglo bacha</t>
-  </si>
-  <si>
     <t>Egresos extraordinarios</t>
   </si>
   <si>
-    <t>Recarga anual de matafuegos</t>
-  </si>
-  <si>
     <t>AUMENTADOS EN 0ct 2025</t>
   </si>
   <si>
     <t>Estefania</t>
   </si>
   <si>
-    <t>Expensas extraordinarias jun 2024</t>
-  </si>
-  <si>
     <t>Expensas extr.</t>
   </si>
   <si>
-    <t>Intereses (3% c/ mes)</t>
-  </si>
-  <si>
     <t>Liquidación de mes</t>
   </si>
   <si>
@@ -305,6 +284,15 @@
   </si>
   <si>
     <t>Recarga de matafuegos-  Matafuegos FIRE</t>
+  </si>
+  <si>
+    <t>Colocacion de membarana en techo - A dos aguas - Material y mano de obra</t>
+  </si>
+  <si>
+    <t>SALDO</t>
+  </si>
+  <si>
+    <t>Ingresos extraordinarios</t>
   </si>
 </sst>
 </file>
@@ -844,7 +832,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="125">
+  <cellXfs count="128">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1005,12 +993,30 @@
     <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="1" fillId="3" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="25" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -1032,21 +1038,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="25" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1062,8 +1053,10 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="16" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="16" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="11" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="11" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -1431,17 +1424,17 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:H58"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A2:H56"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
-    <col min="2" max="2" width="40.33203125" customWidth="1"/>
-    <col min="3" max="3" width="16.44140625" customWidth="1"/>
-    <col min="4" max="4" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="40.28515625" customWidth="1"/>
+    <col min="3" max="3" width="16.42578125" customWidth="1"/>
+    <col min="4" max="4" width="12.140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>17</v>
       </c>
@@ -1449,43 +1442,43 @@
         <v>61</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B4" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3"/>
       <c r="B5" s="21"/>
       <c r="C5" s="3"/>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="22" t="s">
         <v>35</v>
       </c>
       <c r="B7" s="23" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="C7" s="23" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="3"/>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>37</v>
       </c>
@@ -1493,7 +1486,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>38</v>
       </c>
@@ -1501,37 +1494,37 @@
         <v>46</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="19" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="53" t="s">
         <v>12</v>
       </c>
       <c r="B16" s="46"/>
       <c r="C16" s="84"/>
     </row>
-    <row r="17" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="46" t="s">
         <v>49</v>
       </c>
       <c r="B17" s="54" t="s">
-        <v>74</v>
-      </c>
-      <c r="C17" s="123">
+        <v>73</v>
+      </c>
+      <c r="C17" s="51">
         <v>43870.01</v>
       </c>
       <c r="D17" s="5"/>
       <c r="E17" s="12"/>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="46" t="s">
         <v>62</v>
       </c>
@@ -1542,14 +1535,14 @@
       <c r="D18" s="38"/>
       <c r="E18" s="12"/>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="46" t="s">
         <v>42</v>
       </c>
       <c r="B19" s="56" t="s">
         <v>65</v>
       </c>
-      <c r="C19" s="123">
+      <c r="C19" s="51">
         <v>20706.509999999998</v>
       </c>
       <c r="D19" s="5"/>
@@ -1557,21 +1550,19 @@
       <c r="F19" s="14"/>
       <c r="H19" s="86"/>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="46" t="s">
         <v>31</v>
       </c>
-      <c r="B20" s="56" t="s">
-        <v>75</v>
-      </c>
+      <c r="B20" s="56"/>
       <c r="C20" s="100">
-        <v>168796.55</v>
+        <v>162865.29999999999</v>
       </c>
       <c r="D20" s="38"/>
       <c r="F20" s="12"/>
       <c r="H20" s="86"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="46" t="s">
         <v>32</v>
       </c>
@@ -1584,30 +1575,30 @@
       <c r="D21" s="5"/>
       <c r="E21" s="12"/>
       <c r="H21" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="57"/>
       <c r="B22" s="58"/>
       <c r="C22" s="42">
         <f>SUM(C17:C21)</f>
-        <v>291357.82</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+        <v>285426.57</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="53" t="s">
         <v>33</v>
       </c>
       <c r="B23" s="56"/>
       <c r="C23" s="84"/>
     </row>
-    <row r="24" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" s="46" t="s">
         <v>63</v>
       </c>
       <c r="B24" s="59" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="C24" s="51">
         <f>68460+68460*5%</f>
@@ -1615,262 +1606,242 @@
       </c>
       <c r="F24" s="18"/>
     </row>
-    <row r="25" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A25" s="46" t="s">
-        <v>80</v>
+    <row r="25" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A25" s="124" t="s">
+        <v>86</v>
       </c>
       <c r="B25" s="59"/>
       <c r="C25" s="51">
+        <v>180000</v>
+      </c>
+      <c r="F25" s="18"/>
+    </row>
+    <row r="26" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A26" s="46" t="s">
+        <v>85</v>
+      </c>
+      <c r="B26" s="59"/>
+      <c r="C26" s="51">
         <v>60899.97</v>
       </c>
-      <c r="F25" s="18"/>
-    </row>
-    <row r="26" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A26" s="124"/>
-      <c r="B26" s="59"/>
-      <c r="C26" s="123">
-        <v>180000</v>
-      </c>
       <c r="F26" s="18"/>
     </row>
-    <row r="27" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" s="46" t="s">
-        <v>92</v>
-      </c>
-      <c r="B27" s="59"/>
-      <c r="C27" s="123">
-        <v>60899.97</v>
-      </c>
+        <v>68</v>
+      </c>
+      <c r="B27" s="56"/>
+      <c r="C27" s="52"/>
+      <c r="D27" s="5"/>
+      <c r="E27" s="12"/>
       <c r="F27" s="18"/>
     </row>
-    <row r="28" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A28" s="46" t="s">
-        <v>69</v>
-      </c>
-      <c r="B28" s="56"/>
-      <c r="C28" s="52"/>
-      <c r="D28" s="5"/>
-      <c r="E28" s="12"/>
+    <row r="28" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A28" s="57"/>
+      <c r="B28" s="58"/>
+      <c r="C28" s="42">
+        <f>SUM(C23:C27)</f>
+        <v>312782.96999999997</v>
+      </c>
       <c r="F28" s="18"/>
     </row>
-    <row r="29" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A29" s="57"/>
-      <c r="B29" s="58"/>
-      <c r="C29" s="42">
-        <f>SUM(C23:C28)</f>
-        <v>373682.93999999994</v>
+    <row r="29" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A29" s="49" t="s">
+        <v>67</v>
+      </c>
+      <c r="B29" s="49"/>
+      <c r="C29" s="60">
+        <f>+C28+C22</f>
+        <v>598209.54</v>
       </c>
       <c r="F29" s="18"/>
     </row>
-    <row r="30" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A30" s="49" t="s">
-        <v>68</v>
-      </c>
-      <c r="B30" s="49"/>
-      <c r="C30" s="60">
-        <f>+C29+C22</f>
-        <v>665040.76</v>
-      </c>
+    <row r="30" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="C30" s="43"/>
       <c r="F30" s="18"/>
     </row>
-    <row r="31" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A31" s="19" t="s">
+        <v>43</v>
+      </c>
       <c r="C31" s="43"/>
       <c r="F31" s="18"/>
     </row>
-    <row r="32" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A32" s="19" t="s">
-        <v>43</v>
-      </c>
-      <c r="C32" s="43"/>
+    <row r="32" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A32" s="105"/>
+      <c r="B32" s="106"/>
+      <c r="C32" s="101"/>
       <c r="F32" s="18"/>
     </row>
-    <row r="33" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A33" s="104" t="s">
-        <v>77</v>
-      </c>
-      <c r="B33" s="105"/>
-      <c r="C33" s="101">
-        <f>68000+40000</f>
-        <v>108000</v>
-      </c>
+    <row r="33" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A33" s="46"/>
+      <c r="B33" s="46"/>
+      <c r="C33" s="52"/>
       <c r="F33" s="18"/>
     </row>
-    <row r="34" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34" s="46"/>
       <c r="B34" s="46"/>
       <c r="C34" s="52"/>
       <c r="F34" s="18"/>
     </row>
-    <row r="35" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A35" s="46"/>
-      <c r="B35" s="46"/>
-      <c r="C35" s="52"/>
+    <row r="35" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="C35" s="44"/>
       <c r="F35" s="18"/>
     </row>
-    <row r="36" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="C36" s="44"/>
-      <c r="F36" s="18"/>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" s="19" t="s">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="B37" s="19"/>
-      <c r="C37" s="20">
-        <f>+C33+C34+C35+C36</f>
-        <v>108000</v>
-      </c>
-      <c r="E37" s="12"/>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A39" s="29" t="s">
+      <c r="B36" s="19"/>
+      <c r="C36" s="20">
+        <f>+C32+C33+C34+C35</f>
+        <v>0</v>
+      </c>
+      <c r="E36" s="12"/>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="B39" s="29"/>
-      <c r="C39" s="30">
-        <f>+C37+C30</f>
-        <v>773040.76</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A41" s="5" t="s">
+      <c r="B38" s="29"/>
+      <c r="C38" s="30">
+        <f>+C36+C29</f>
+        <v>598209.54</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="5" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A42" s="31" t="s">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="B42" s="28"/>
-      <c r="C42" s="33">
-        <v>283181.4519533891</v>
-      </c>
-      <c r="D42" s="6"/>
-      <c r="E42" s="6"/>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B41" s="28"/>
+      <c r="C41" s="33">
+        <v>66868.53562338918</v>
+      </c>
+      <c r="D41" s="6"/>
+      <c r="E41" s="6"/>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>8</v>
+      </c>
+      <c r="C42" s="27">
+        <f>'prorrateo '!F13</f>
+        <v>419434.17550000001</v>
+      </c>
+      <c r="D42" s="12"/>
+      <c r="E42" s="12"/>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>8</v>
-      </c>
-      <c r="C43" s="27">
-        <f>'prorrateo '!F13</f>
-        <v>344315.93367</v>
+        <v>88</v>
+      </c>
+      <c r="C43" s="126">
+        <f>extraordinarias!E13</f>
+        <v>26352</v>
       </c>
       <c r="D43" s="12"/>
       <c r="E43" s="12"/>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>67</v>
-      </c>
-      <c r="C44" s="61"/>
+        <v>75</v>
+      </c>
+      <c r="C44" s="61">
+        <f>-C36</f>
+        <v>0</v>
+      </c>
       <c r="D44" s="12"/>
       <c r="E44" s="12"/>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="C45" s="61">
-        <v>-20000</v>
-      </c>
-      <c r="D45" s="12"/>
-      <c r="E45" s="12"/>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A46" t="s">
-        <v>79</v>
-      </c>
-      <c r="C46" s="61">
-        <f>-C37</f>
-        <v>-108000</v>
-      </c>
-      <c r="D46" s="12"/>
-      <c r="E46" s="12"/>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A47" t="s">
-        <v>66</v>
-      </c>
-      <c r="C47" s="61">
-        <f>-(C30-C28)</f>
-        <v>-665040.76</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A48" s="31" t="s">
+        <f>-(C29-C27)</f>
+        <v>-598209.54</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" s="31" t="s">
         <v>15</v>
       </c>
-      <c r="B48" s="28"/>
-      <c r="C48" s="33">
-        <f>SUM(C42:C47)</f>
-        <v>-165543.37437661085</v>
-      </c>
-      <c r="D48" s="6"/>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B46" s="28"/>
+      <c r="C46" s="33">
+        <f>SUM(C41:C45)</f>
+        <v>-85554.828876610845</v>
+      </c>
+      <c r="D46" s="6"/>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" s="15"/>
+      <c r="B47" s="14"/>
+      <c r="C47" s="16"/>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" s="15"/>
+      <c r="B48" s="14"/>
+      <c r="C48" s="16"/>
+      <c r="F48" s="62"/>
+    </row>
+    <row r="49" spans="1:3" ht="2.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="15"/>
       <c r="B49" s="14"/>
       <c r="C49" s="16"/>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A50" s="15"/>
-      <c r="B50" s="14"/>
-      <c r="C50" s="16"/>
-      <c r="F50" s="62"/>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A51" s="15"/>
-      <c r="B51" s="14"/>
-      <c r="C51" s="16"/>
-    </row>
-    <row r="52" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A52" s="45" t="s">
+    <row r="50" spans="1:3" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="45" t="s">
         <v>60</v>
       </c>
-      <c r="B52" s="64"/>
-      <c r="C52" s="65">
+      <c r="B50" s="64"/>
+      <c r="C50" s="65">
         <v>109834.99657000002</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A53" s="46"/>
-      <c r="B53" s="46"/>
-      <c r="C53" s="50"/>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A54" s="49" t="s">
+    <row r="51" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="46"/>
+      <c r="B51" s="46"/>
+      <c r="C51" s="50"/>
+    </row>
+    <row r="52" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="49" t="s">
         <v>4</v>
       </c>
-      <c r="B54" s="47"/>
-      <c r="C54" s="48">
-        <f>SUM(C52:C53)</f>
+      <c r="B52" s="47"/>
+      <c r="C52" s="48">
+        <f>SUM(C50:C51)</f>
         <v>109834.99657000002</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" s="14"/>
+      <c r="B53" s="14"/>
+      <c r="C53" s="14"/>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54" s="14"/>
+      <c r="B54" s="14"/>
+      <c r="C54" s="14"/>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" s="14"/>
       <c r="B55" s="14"/>
       <c r="C55" s="14"/>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" s="14"/>
       <c r="B56" s="14"/>
       <c r="C56" s="14"/>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A57" s="14"/>
-      <c r="B57" s="14"/>
-      <c r="C57" s="14"/>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A58" s="14"/>
-      <c r="B58" s="14"/>
-      <c r="C58" s="14"/>
-    </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="A32:B32"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="B4" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
@@ -1888,36 +1859,36 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Q39"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.33203125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="5.28515625" style="1" customWidth="1"/>
     <col min="2" max="2" width="8" style="1" customWidth="1"/>
-    <col min="3" max="3" width="23.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.33203125" customWidth="1"/>
-    <col min="6" max="6" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.44140625" customWidth="1"/>
-    <col min="8" max="8" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.44140625" customWidth="1"/>
-    <col min="10" max="10" width="9.109375" customWidth="1"/>
-    <col min="11" max="12" width="12.44140625" customWidth="1"/>
-    <col min="13" max="13" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11.44140625" style="17"/>
+    <col min="3" max="3" width="23.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.28515625" customWidth="1"/>
+    <col min="6" max="6" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.42578125" customWidth="1"/>
+    <col min="8" max="8" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.42578125" customWidth="1"/>
+    <col min="10" max="10" width="9.140625" customWidth="1"/>
+    <col min="11" max="12" width="12.42578125" customWidth="1"/>
+    <col min="13" max="13" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.42578125" style="17"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="40" t="s">
         <v>47</v>
       </c>
       <c r="E1" s="103">
-        <v>432628.85</v>
+        <v>598209.54</v>
       </c>
       <c r="G1" t="str">
         <f>'detalle y gastos'!C7</f>
         <v>Vto. 15/12</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" s="71" t="str">
         <f>'detalle y gastos'!B7</f>
         <v>LIQUIDACIÓN EXPENSAS NOVIEMBRE 2025</v>
@@ -1937,61 +1908,61 @@
       <c r="L2" s="66"/>
       <c r="M2" s="67"/>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A3" s="116"/>
-      <c r="B3" s="113" t="s">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A3" s="110"/>
+      <c r="B3" s="108" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="110" t="s">
+      <c r="C3" s="116" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="111" t="s">
+      <c r="D3" s="117" t="s">
         <v>54</v>
       </c>
-      <c r="E3" s="113" t="s">
+      <c r="E3" s="108" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="108" t="s">
+      <c r="F3" s="114" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="110" t="s">
+      <c r="G3" s="116" t="s">
         <v>52</v>
       </c>
-      <c r="H3" s="108" t="s">
+      <c r="H3" s="114" t="s">
         <v>44</v>
       </c>
-      <c r="I3" s="110" t="s">
+      <c r="I3" s="116" t="s">
         <v>6</v>
       </c>
-      <c r="J3" s="112" t="s">
-        <v>87</v>
-      </c>
-      <c r="K3" s="106" t="s">
+      <c r="J3" s="118" t="s">
+        <v>80</v>
+      </c>
+      <c r="K3" s="112" t="s">
+        <v>69</v>
+      </c>
+      <c r="L3" s="112" t="s">
         <v>70</v>
       </c>
-      <c r="L3" s="106" t="s">
+      <c r="M3" s="112" t="s">
         <v>71</v>
       </c>
-      <c r="M3" s="106" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A4" s="117"/>
-      <c r="B4" s="114"/>
-      <c r="C4" s="110"/>
-      <c r="D4" s="111"/>
-      <c r="E4" s="114"/>
-      <c r="F4" s="109"/>
-      <c r="G4" s="110"/>
-      <c r="H4" s="109"/>
-      <c r="I4" s="110"/>
-      <c r="J4" s="112"/>
-      <c r="K4" s="107"/>
-      <c r="L4" s="107"/>
-      <c r="M4" s="107"/>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A4" s="111"/>
+      <c r="B4" s="109"/>
+      <c r="C4" s="116"/>
+      <c r="D4" s="117"/>
+      <c r="E4" s="109"/>
+      <c r="F4" s="115"/>
+      <c r="G4" s="116"/>
+      <c r="H4" s="115"/>
+      <c r="I4" s="116"/>
+      <c r="J4" s="118"/>
+      <c r="K4" s="113"/>
+      <c r="L4" s="113"/>
+      <c r="M4" s="113"/>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" s="68">
         <v>1</v>
       </c>
@@ -2005,14 +1976,14 @@
         <v>58</v>
       </c>
       <c r="E5" s="37">
-        <v>47997.627809999998</v>
-      </c>
-      <c r="F5" s="85">
-        <v>48000</v>
+        <v>52345.718659999991</v>
+      </c>
+      <c r="F5" s="125">
+        <v>52350</v>
       </c>
       <c r="G5" s="37">
         <f>E5-F5</f>
-        <v>-2.372190000001865</v>
+        <v>-4.2813400000086403</v>
       </c>
       <c r="H5" s="37">
         <f>IF(G5&gt;0,G5*3%,0)</f>
@@ -2024,18 +1995,18 @@
       <c r="J5" s="63"/>
       <c r="K5" s="75">
         <f>E1*I5</f>
-        <v>52348.090849999993</v>
+        <v>72383.354340000005</v>
       </c>
       <c r="L5" s="75">
         <f>E5-F5+H5+K5+J5</f>
-        <v>52345.718659999991</v>
+        <v>72379.073000000004</v>
       </c>
       <c r="M5" s="76">
         <f>L5+L5*4%</f>
-        <v>54439.547406399994</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
+        <v>75274.235920000006</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" s="68">
         <v>2</v>
       </c>
@@ -2049,11 +2020,11 @@
         <v>59</v>
       </c>
       <c r="E6" s="37">
-        <v>48394.30242</v>
-      </c>
-      <c r="F6" s="85">
+        <v>52780.719699999994</v>
+      </c>
+      <c r="F6" s="125">
         <f t="shared" ref="F6:F11" si="0">E6</f>
-        <v>48394.30242</v>
+        <v>52780.719699999994</v>
       </c>
       <c r="G6" s="37">
         <f t="shared" ref="G6:G12" si="1">E6-F6</f>
@@ -2069,20 +2040,20 @@
       <c r="J6" s="63"/>
       <c r="K6" s="75">
         <f>E1*I6</f>
-        <v>52780.719699999994</v>
+        <v>72981.563880000002</v>
       </c>
       <c r="L6" s="75">
         <f t="shared" ref="L6:L12" si="3">E6-F6+H6+K6+J6</f>
-        <v>52780.719699999994</v>
+        <v>72981.563880000002</v>
       </c>
       <c r="M6" s="76">
         <f t="shared" ref="M6:M12" si="4">L6+L6*4%</f>
-        <v>54891.948487999995</v>
+        <v>75900.826435199997</v>
       </c>
       <c r="O6" s="83"/>
       <c r="Q6" s="82"/>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" s="68">
         <v>3</v>
       </c>
@@ -2093,18 +2064,17 @@
         <v>28</v>
       </c>
       <c r="D7" s="41" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E7" s="37">
-        <v>46410.929369999998</v>
-      </c>
-      <c r="F7" s="85">
-        <f t="shared" si="0"/>
-        <v>46410.929369999998</v>
+        <v>50617.575449999997</v>
+      </c>
+      <c r="F7" s="125">
+        <v>94528</v>
       </c>
       <c r="G7" s="37">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-43910.424550000003</v>
       </c>
       <c r="H7" s="37">
         <f t="shared" si="2"/>
@@ -2116,18 +2086,18 @@
       <c r="J7" s="63"/>
       <c r="K7" s="75">
         <f>E1*I7</f>
-        <v>50617.575449999997</v>
+        <v>69990.516180000006</v>
       </c>
       <c r="L7" s="75">
         <f t="shared" si="3"/>
-        <v>50617.575449999997</v>
+        <v>26080.091630000003</v>
       </c>
       <c r="M7" s="76">
         <f t="shared" si="4"/>
-        <v>52642.278467999997</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
+        <v>27123.295295200001</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" s="68">
         <v>4</v>
       </c>
@@ -2138,14 +2108,14 @@
         <v>29</v>
       </c>
       <c r="D8" s="41" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E8" s="85">
-        <v>46410.929369999998</v>
-      </c>
-      <c r="F8" s="85">
+        <v>50617.575449999997</v>
+      </c>
+      <c r="F8" s="127">
         <f>E8</f>
-        <v>46410.929369999998</v>
+        <v>50617.575449999997</v>
       </c>
       <c r="G8" s="37">
         <f t="shared" si="1"/>
@@ -2161,18 +2131,18 @@
       <c r="J8" s="63"/>
       <c r="K8" s="75">
         <f>E1*I8</f>
-        <v>50617.575449999997</v>
+        <v>69990.516180000006</v>
       </c>
       <c r="L8" s="75">
         <f t="shared" si="3"/>
-        <v>50617.575449999997</v>
+        <v>69990.516180000006</v>
       </c>
       <c r="M8" s="76">
         <f t="shared" si="4"/>
-        <v>52642.278467999997</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
+        <v>72790.136827200011</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="68">
         <v>5</v>
       </c>
@@ -2186,11 +2156,11 @@
         <v>57</v>
       </c>
       <c r="E9" s="37">
-        <v>54344.421570000006</v>
-      </c>
-      <c r="F9" s="85">
+        <v>59270.152450000001</v>
+      </c>
+      <c r="F9" s="125">
         <f>E9</f>
-        <v>54344.421570000006</v>
+        <v>59270.152450000001</v>
       </c>
       <c r="G9" s="37">
         <f t="shared" si="1"/>
@@ -2206,18 +2176,18 @@
       <c r="J9" s="63"/>
       <c r="K9" s="75">
         <f>E1*I9</f>
-        <v>59270.152450000001</v>
+        <v>81954.706980000017</v>
       </c>
       <c r="L9" s="75">
         <f t="shared" si="3"/>
-        <v>59270.152450000001</v>
+        <v>81954.706980000017</v>
       </c>
       <c r="M9" s="76">
         <f t="shared" si="4"/>
-        <v>61640.958548000002</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
+        <v>85232.895259200013</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" s="68">
         <v>6</v>
       </c>
@@ -2228,40 +2198,38 @@
         <v>26</v>
       </c>
       <c r="D10" s="41" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="E10" s="37">
-        <v>99619.343603999994</v>
+        <v>179714.93211211998</v>
       </c>
       <c r="F10" s="85"/>
       <c r="G10" s="37">
         <f t="shared" si="1"/>
-        <v>99619.343603999994</v>
+        <v>179714.93211211998</v>
       </c>
       <c r="H10" s="37">
         <f t="shared" si="2"/>
-        <v>2988.5803081199997</v>
+        <v>5391.4479633635992</v>
       </c>
       <c r="I10" s="74">
         <v>0.13200000000000001</v>
       </c>
-      <c r="J10" s="63">
-        <v>20000</v>
-      </c>
+      <c r="J10" s="63"/>
       <c r="K10" s="75">
         <f>E1*I10</f>
-        <v>57107.008199999997</v>
+        <v>78963.659280000007</v>
       </c>
       <c r="L10" s="75">
         <f t="shared" si="3"/>
-        <v>179714.93211211998</v>
+        <v>264070.0393554836</v>
       </c>
       <c r="M10" s="76">
         <f t="shared" si="4"/>
-        <v>186903.52939660478</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
+        <v>274632.84092970297</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" s="68">
         <v>7</v>
       </c>
@@ -2275,11 +2243,11 @@
         <v>56</v>
       </c>
       <c r="E11" s="37">
-        <v>50377.675470000002</v>
-      </c>
-      <c r="F11" s="85">
+        <v>54943.863949999999</v>
+      </c>
+      <c r="F11" s="125">
         <f t="shared" si="0"/>
-        <v>50377.675470000002</v>
+        <v>54943.863949999999</v>
       </c>
       <c r="G11" s="37">
         <f t="shared" si="1"/>
@@ -2295,18 +2263,18 @@
       <c r="J11" s="63"/>
       <c r="K11" s="75">
         <f>E1*I11</f>
-        <v>54943.863949999999</v>
+        <v>75972.611580000012</v>
       </c>
       <c r="L11" s="75">
         <f t="shared" si="3"/>
-        <v>54943.863949999999</v>
+        <v>75972.611580000012</v>
       </c>
       <c r="M11" s="76">
         <f t="shared" si="4"/>
-        <v>57141.618508</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
+        <v>79011.516043200012</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" s="68">
         <v>8</v>
       </c>
@@ -2320,11 +2288,11 @@
         <v>55</v>
       </c>
       <c r="E12" s="37">
-        <v>50377.675470000002</v>
-      </c>
-      <c r="F12" s="85">
+        <v>54943.863949999999</v>
+      </c>
+      <c r="F12" s="125">
         <f>E12</f>
-        <v>50377.675470000002</v>
+        <v>54943.863949999999</v>
       </c>
       <c r="G12" s="37">
         <f t="shared" si="1"/>
@@ -2340,18 +2308,18 @@
       <c r="J12" s="63"/>
       <c r="K12" s="75">
         <f>E1*I12</f>
-        <v>54943.863949999999</v>
+        <v>75972.611580000012</v>
       </c>
       <c r="L12" s="75">
         <f t="shared" si="3"/>
-        <v>54943.863949999999</v>
+        <v>75972.611580000012</v>
       </c>
       <c r="M12" s="76">
         <f t="shared" si="4"/>
-        <v>57141.618508</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>79011.516043200012</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="77" t="s">
         <v>10</v>
       </c>
@@ -2360,16 +2328,16 @@
       <c r="D13" s="79"/>
       <c r="E13" s="80">
         <f>SUM(E5:E12)</f>
-        <v>443932.90508400003</v>
+        <v>555234.40172212</v>
       </c>
       <c r="F13" s="69">
         <f>SUM(F5:F12)</f>
-        <v>344315.93367</v>
+        <v>419434.17550000001</v>
       </c>
       <c r="G13" s="69"/>
       <c r="H13" s="69">
         <f>SUM(H5:H12)</f>
-        <v>2988.5803081199997</v>
+        <v>5391.4479633635992</v>
       </c>
       <c r="I13" s="70">
         <f t="shared" ref="I13" si="5">SUM(I5:I12)</f>
@@ -2377,359 +2345,354 @@
       </c>
       <c r="J13" s="102">
         <f>SUM(J5:J12)</f>
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="K13" s="80">
         <f>SUM(K5:K12)</f>
-        <v>432628.85</v>
+        <v>598209.54</v>
       </c>
       <c r="L13" s="80">
         <f>SUM(L5:L12)</f>
-        <v>555234.40172212</v>
+        <v>739401.21418548375</v>
       </c>
       <c r="M13" s="81">
         <f>SUM(M5:M12)</f>
-        <v>577443.77779100474</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="C15" s="115" t="s">
-        <v>88</v>
-      </c>
-      <c r="D15" s="115"/>
-      <c r="E15" s="115"/>
-      <c r="F15" s="115"/>
-      <c r="G15" s="115"/>
-      <c r="H15" s="115"/>
-      <c r="I15" s="115"/>
-      <c r="J15" s="115"/>
-      <c r="K15" s="115"/>
-      <c r="L15" s="115"/>
-    </row>
-    <row r="16" spans="1:17" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+        <v>768977.26275290304</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="C15" s="107" t="s">
+        <v>81</v>
+      </c>
+      <c r="D15" s="107"/>
+      <c r="E15" s="107"/>
+      <c r="F15" s="107"/>
+      <c r="G15" s="107"/>
+      <c r="H15" s="107"/>
+      <c r="I15" s="107"/>
+      <c r="J15" s="107"/>
+      <c r="K15" s="107"/>
+      <c r="L15" s="107"/>
+    </row>
+    <row r="16" spans="1:17" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="40" t="s">
         <v>48</v>
       </c>
-      <c r="C16" s="115"/>
-      <c r="D16" s="115"/>
-      <c r="E16" s="115"/>
-      <c r="F16" s="115"/>
-      <c r="G16" s="115"/>
-      <c r="H16" s="115"/>
-      <c r="I16" s="115"/>
-      <c r="J16" s="115"/>
-      <c r="K16" s="115"/>
-      <c r="L16" s="115"/>
-    </row>
-    <row r="17" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C16" s="107"/>
+      <c r="D16" s="107"/>
+      <c r="E16" s="107"/>
+      <c r="F16" s="107"/>
+      <c r="G16" s="107"/>
+      <c r="H16" s="107"/>
+      <c r="I16" s="107"/>
+      <c r="J16" s="107"/>
+      <c r="K16" s="107"/>
+      <c r="L16" s="107"/>
+    </row>
+    <row r="17" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="24" t="s">
         <v>50</v>
       </c>
       <c r="B17" s="25"/>
-      <c r="C17" s="115"/>
-      <c r="D17" s="115"/>
-      <c r="E17" s="115"/>
-      <c r="F17" s="115"/>
-      <c r="G17" s="115"/>
-      <c r="H17" s="115"/>
-      <c r="I17" s="115"/>
-      <c r="J17" s="115"/>
-      <c r="K17" s="115"/>
-      <c r="L17" s="115"/>
+      <c r="C17" s="107"/>
+      <c r="D17" s="107"/>
+      <c r="E17" s="107"/>
+      <c r="F17" s="107"/>
+      <c r="G17" s="107"/>
+      <c r="H17" s="107"/>
+      <c r="I17" s="107"/>
+      <c r="J17" s="107"/>
+      <c r="K17" s="107"/>
+      <c r="L17" s="107"/>
       <c r="M17" s="26"/>
     </row>
-    <row r="18" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B18" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C18" s="115"/>
-      <c r="D18" s="115"/>
-      <c r="E18" s="115"/>
-      <c r="F18" s="115"/>
-      <c r="G18" s="115"/>
-      <c r="H18" s="115"/>
-      <c r="I18" s="115"/>
-      <c r="J18" s="115"/>
-      <c r="K18" s="115"/>
-      <c r="L18" s="115"/>
+      <c r="C18" s="107"/>
+      <c r="D18" s="107"/>
+      <c r="E18" s="107"/>
+      <c r="F18" s="107"/>
+      <c r="G18" s="107"/>
+      <c r="H18" s="107"/>
+      <c r="I18" s="107"/>
+      <c r="J18" s="107"/>
+      <c r="K18" s="107"/>
+      <c r="L18" s="107"/>
       <c r="M18" s="36" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2"/>
       <c r="B19" s="7"/>
-      <c r="C19" s="115"/>
-      <c r="D19" s="115"/>
-      <c r="E19" s="115"/>
-      <c r="F19" s="115"/>
-      <c r="G19" s="115"/>
-      <c r="H19" s="115"/>
-      <c r="I19" s="115"/>
-      <c r="J19" s="115"/>
-      <c r="K19" s="115"/>
-      <c r="L19" s="115"/>
+      <c r="C19" s="107"/>
+      <c r="D19" s="107"/>
+      <c r="E19" s="107"/>
+      <c r="F19" s="107"/>
+      <c r="G19" s="107"/>
+      <c r="H19" s="107"/>
+      <c r="I19" s="107"/>
+      <c r="J19" s="107"/>
+      <c r="K19" s="107"/>
+      <c r="L19" s="107"/>
       <c r="M19" s="32" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="10">
         <v>1</v>
       </c>
       <c r="B20" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="C20" s="115"/>
-      <c r="D20" s="115"/>
-      <c r="E20" s="115"/>
-      <c r="F20" s="115"/>
-      <c r="G20" s="115"/>
-      <c r="H20" s="115"/>
-      <c r="I20" s="115"/>
-      <c r="J20" s="115"/>
-      <c r="K20" s="115"/>
-      <c r="L20" s="115"/>
+      <c r="C20" s="107"/>
+      <c r="D20" s="107"/>
+      <c r="E20" s="107"/>
+      <c r="F20" s="107"/>
+      <c r="G20" s="107"/>
+      <c r="H20" s="107"/>
+      <c r="I20" s="107"/>
+      <c r="J20" s="107"/>
+      <c r="K20" s="107"/>
+      <c r="L20" s="107"/>
       <c r="M20" s="34" t="e">
         <f>+#REF!+H20+K20</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="21" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="10">
         <v>2</v>
       </c>
       <c r="B21" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="C21" s="115"/>
-      <c r="D21" s="115"/>
-      <c r="E21" s="115"/>
-      <c r="F21" s="115"/>
-      <c r="G21" s="115"/>
-      <c r="H21" s="115"/>
-      <c r="I21" s="115"/>
-      <c r="J21" s="115"/>
-      <c r="K21" s="115"/>
-      <c r="L21" s="115"/>
+      <c r="C21" s="107"/>
+      <c r="D21" s="107"/>
+      <c r="E21" s="107"/>
+      <c r="F21" s="107"/>
+      <c r="G21" s="107"/>
+      <c r="H21" s="107"/>
+      <c r="I21" s="107"/>
+      <c r="J21" s="107"/>
+      <c r="K21" s="107"/>
+      <c r="L21" s="107"/>
       <c r="M21" s="34" t="e">
         <f>+#REF!+H21+K21</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="22" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="10">
         <v>3</v>
       </c>
       <c r="B22" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="C22" s="115"/>
-      <c r="D22" s="115"/>
-      <c r="E22" s="115"/>
-      <c r="F22" s="115"/>
-      <c r="G22" s="115"/>
-      <c r="H22" s="115"/>
-      <c r="I22" s="115"/>
-      <c r="J22" s="115"/>
-      <c r="K22" s="115"/>
-      <c r="L22" s="115"/>
+      <c r="C22" s="107"/>
+      <c r="D22" s="107"/>
+      <c r="E22" s="107"/>
+      <c r="F22" s="107"/>
+      <c r="G22" s="107"/>
+      <c r="H22" s="107"/>
+      <c r="I22" s="107"/>
+      <c r="J22" s="107"/>
+      <c r="K22" s="107"/>
+      <c r="L22" s="107"/>
       <c r="M22" s="34" t="e">
         <f>+#REF!+H22+K22</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="23" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="10">
         <v>4</v>
       </c>
       <c r="B23" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="C23" s="115"/>
-      <c r="D23" s="115"/>
-      <c r="E23" s="115"/>
-      <c r="F23" s="115"/>
-      <c r="G23" s="115"/>
-      <c r="H23" s="115"/>
-      <c r="I23" s="115"/>
-      <c r="J23" s="115"/>
-      <c r="K23" s="115"/>
-      <c r="L23" s="115"/>
+      <c r="C23" s="107"/>
+      <c r="D23" s="107"/>
+      <c r="E23" s="107"/>
+      <c r="F23" s="107"/>
+      <c r="G23" s="107"/>
+      <c r="H23" s="107"/>
+      <c r="I23" s="107"/>
+      <c r="J23" s="107"/>
+      <c r="K23" s="107"/>
+      <c r="L23" s="107"/>
       <c r="M23" s="34" t="e">
         <f>+#REF!+H23+K23</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="24" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="10">
         <v>5</v>
       </c>
       <c r="B24" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="C24" s="115"/>
-      <c r="D24" s="115"/>
-      <c r="E24" s="115"/>
-      <c r="F24" s="115"/>
-      <c r="G24" s="115"/>
-      <c r="H24" s="115"/>
-      <c r="I24" s="115"/>
-      <c r="J24" s="115"/>
-      <c r="K24" s="115"/>
-      <c r="L24" s="115"/>
+      <c r="C24" s="107"/>
+      <c r="D24" s="107"/>
+      <c r="E24" s="107"/>
+      <c r="F24" s="107"/>
+      <c r="G24" s="107"/>
+      <c r="H24" s="107"/>
+      <c r="I24" s="107"/>
+      <c r="J24" s="107"/>
+      <c r="K24" s="107"/>
+      <c r="L24" s="107"/>
       <c r="M24" s="34" t="e">
         <f>+#REF!+H24+K24</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="25" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="10">
         <v>6</v>
       </c>
       <c r="B25" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="C25" s="115"/>
-      <c r="D25" s="115"/>
-      <c r="E25" s="115"/>
-      <c r="F25" s="115"/>
-      <c r="G25" s="115"/>
-      <c r="H25" s="115"/>
-      <c r="I25" s="115"/>
-      <c r="J25" s="115"/>
-      <c r="K25" s="115"/>
-      <c r="L25" s="115"/>
+      <c r="C25" s="107"/>
+      <c r="D25" s="107"/>
+      <c r="E25" s="107"/>
+      <c r="F25" s="107"/>
+      <c r="G25" s="107"/>
+      <c r="H25" s="107"/>
+      <c r="I25" s="107"/>
+      <c r="J25" s="107"/>
+      <c r="K25" s="107"/>
+      <c r="L25" s="107"/>
       <c r="M25" s="34" t="e">
         <f>+#REF!+H25+K25</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="26" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="10">
         <v>7</v>
       </c>
       <c r="B26" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="C26" s="115"/>
-      <c r="D26" s="115"/>
-      <c r="E26" s="115"/>
-      <c r="F26" s="115"/>
-      <c r="G26" s="115"/>
-      <c r="H26" s="115"/>
-      <c r="I26" s="115"/>
-      <c r="J26" s="115"/>
-      <c r="K26" s="115"/>
-      <c r="L26" s="115"/>
+      <c r="C26" s="107"/>
+      <c r="D26" s="107"/>
+      <c r="E26" s="107"/>
+      <c r="F26" s="107"/>
+      <c r="G26" s="107"/>
+      <c r="H26" s="107"/>
+      <c r="I26" s="107"/>
+      <c r="J26" s="107"/>
+      <c r="K26" s="107"/>
+      <c r="L26" s="107"/>
       <c r="M26" s="34" t="e">
         <f>+#REF!+H26+K26</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="27" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="10">
         <v>8</v>
       </c>
       <c r="B27" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="C27" s="115"/>
-      <c r="D27" s="115"/>
-      <c r="E27" s="115"/>
-      <c r="F27" s="115"/>
-      <c r="G27" s="115"/>
-      <c r="H27" s="115"/>
-      <c r="I27" s="115"/>
-      <c r="J27" s="115"/>
-      <c r="K27" s="115"/>
-      <c r="L27" s="115"/>
+      <c r="C27" s="107"/>
+      <c r="D27" s="107"/>
+      <c r="E27" s="107"/>
+      <c r="F27" s="107"/>
+      <c r="G27" s="107"/>
+      <c r="H27" s="107"/>
+      <c r="I27" s="107"/>
+      <c r="J27" s="107"/>
+      <c r="K27" s="107"/>
+      <c r="L27" s="107"/>
       <c r="M27" s="34" t="e">
         <f>+#REF!+H27+K27</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="28" spans="1:13" ht="15.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:13" ht="15.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="8" t="s">
         <v>10</v>
       </c>
       <c r="B28" s="9"/>
-      <c r="C28" s="115"/>
-      <c r="D28" s="115"/>
-      <c r="E28" s="115"/>
-      <c r="F28" s="115"/>
-      <c r="G28" s="115"/>
-      <c r="H28" s="115"/>
-      <c r="I28" s="115"/>
-      <c r="J28" s="115"/>
-      <c r="K28" s="115"/>
-      <c r="L28" s="115"/>
+      <c r="C28" s="107"/>
+      <c r="D28" s="107"/>
+      <c r="E28" s="107"/>
+      <c r="F28" s="107"/>
+      <c r="G28" s="107"/>
+      <c r="H28" s="107"/>
+      <c r="I28" s="107"/>
+      <c r="J28" s="107"/>
+      <c r="K28" s="107"/>
+      <c r="L28" s="107"/>
       <c r="M28" s="35" t="e">
         <f>SUM(M20:M27)</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="C29" s="115"/>
-      <c r="D29" s="115"/>
-      <c r="E29" s="115"/>
-      <c r="F29" s="115"/>
-      <c r="G29" s="115"/>
-      <c r="H29" s="115"/>
-      <c r="I29" s="115"/>
-      <c r="J29" s="115"/>
-      <c r="K29" s="115"/>
-      <c r="L29" s="115"/>
-    </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="C30" s="115"/>
-      <c r="D30" s="115"/>
-      <c r="E30" s="115"/>
-      <c r="F30" s="115"/>
-      <c r="G30" s="115"/>
-      <c r="H30" s="115"/>
-      <c r="I30" s="115"/>
-      <c r="J30" s="115"/>
-      <c r="K30" s="115"/>
-      <c r="L30" s="115"/>
-    </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="C31" s="115"/>
-      <c r="D31" s="115"/>
-      <c r="E31" s="115"/>
-      <c r="F31" s="115"/>
-      <c r="G31" s="115"/>
-      <c r="H31" s="115"/>
-      <c r="I31" s="115"/>
-      <c r="J31" s="115"/>
-      <c r="K31" s="115"/>
-      <c r="L31" s="115"/>
-    </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="C32" s="115"/>
-      <c r="D32" s="115"/>
-      <c r="E32" s="115"/>
-      <c r="F32" s="115"/>
-      <c r="G32" s="115"/>
-      <c r="H32" s="115"/>
-      <c r="I32" s="115"/>
-      <c r="J32" s="115"/>
-      <c r="K32" s="115"/>
-      <c r="L32" s="115"/>
-    </row>
-    <row r="39" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="C29" s="107"/>
+      <c r="D29" s="107"/>
+      <c r="E29" s="107"/>
+      <c r="F29" s="107"/>
+      <c r="G29" s="107"/>
+      <c r="H29" s="107"/>
+      <c r="I29" s="107"/>
+      <c r="J29" s="107"/>
+      <c r="K29" s="107"/>
+      <c r="L29" s="107"/>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="C30" s="107"/>
+      <c r="D30" s="107"/>
+      <c r="E30" s="107"/>
+      <c r="F30" s="107"/>
+      <c r="G30" s="107"/>
+      <c r="H30" s="107"/>
+      <c r="I30" s="107"/>
+      <c r="J30" s="107"/>
+      <c r="K30" s="107"/>
+      <c r="L30" s="107"/>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="C31" s="107"/>
+      <c r="D31" s="107"/>
+      <c r="E31" s="107"/>
+      <c r="F31" s="107"/>
+      <c r="G31" s="107"/>
+      <c r="H31" s="107"/>
+      <c r="I31" s="107"/>
+      <c r="J31" s="107"/>
+      <c r="K31" s="107"/>
+      <c r="L31" s="107"/>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="C32" s="107"/>
+      <c r="D32" s="107"/>
+      <c r="E32" s="107"/>
+      <c r="F32" s="107"/>
+      <c r="G32" s="107"/>
+      <c r="H32" s="107"/>
+      <c r="I32" s="107"/>
+      <c r="J32" s="107"/>
+      <c r="K32" s="107"/>
+      <c r="L32" s="107"/>
+    </row>
+    <row r="39" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E39" s="39"/>
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="C15:L32"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="K3:K4"/>
-    <mergeCell ref="L3:L4"/>
     <mergeCell ref="M3:M4"/>
     <mergeCell ref="H3:H4"/>
     <mergeCell ref="F3:F4"/>
@@ -2739,6 +2702,11 @@
     <mergeCell ref="J3:J4"/>
     <mergeCell ref="I3:I4"/>
     <mergeCell ref="E3:E4"/>
+    <mergeCell ref="C15:L32"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="K3:K4"/>
+    <mergeCell ref="L3:L4"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -2749,39 +2717,39 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:L13"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.33203125" customWidth="1"/>
-    <col min="3" max="3" width="14.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.88671875" customWidth="1"/>
-    <col min="5" max="5" width="13.109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="21.33203125" customWidth="1"/>
+    <col min="1" max="1" width="6.28515625" customWidth="1"/>
+    <col min="3" max="3" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.28515625" customWidth="1"/>
+    <col min="5" max="5" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.140625" customWidth="1"/>
     <col min="7" max="7" width="18" customWidth="1"/>
-    <col min="8" max="8" width="8.109375" customWidth="1"/>
-    <col min="9" max="9" width="12" customWidth="1"/>
+    <col min="8" max="8" width="11.140625" customWidth="1"/>
+    <col min="9" max="9" width="14.7109375" customWidth="1"/>
     <col min="10" max="10" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="91" t="s">
         <v>48</v>
       </c>
       <c r="B1" s="92"/>
       <c r="C1" s="93"/>
-      <c r="D1" s="118">
-        <v>108000</v>
-      </c>
-      <c r="E1" s="118"/>
-      <c r="F1" s="93"/>
+      <c r="D1" s="119">
+        <v>0</v>
+      </c>
+      <c r="E1" s="119"/>
+      <c r="F1" s="104"/>
       <c r="G1" s="93"/>
       <c r="H1" s="93"/>
       <c r="I1" s="93"/>
       <c r="J1" s="94"/>
       <c r="L1" s="17"/>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="95" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="B2" s="88"/>
       <c r="C2" s="89"/>
@@ -2789,62 +2757,60 @@
         <v>36</v>
       </c>
       <c r="E2" s="88"/>
-      <c r="F2" s="57" t="s">
-        <v>48</v>
-      </c>
+      <c r="F2" s="88"/>
       <c r="G2" s="88"/>
       <c r="H2" s="88"/>
       <c r="I2" s="88"/>
       <c r="J2" s="96"/>
       <c r="L2" s="17"/>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A3" s="119" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="113" t="s">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" s="120" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="108" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="113" t="s">
+      <c r="C3" s="108" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="111" t="s">
+      <c r="D3" s="117" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="110" t="s">
+      <c r="E3" s="116" t="s">
         <v>51</v>
       </c>
-      <c r="F3" s="111" t="s">
-        <v>83</v>
-      </c>
-      <c r="G3" s="111" t="s">
-        <v>85</v>
-      </c>
-      <c r="H3" s="110" t="s">
+      <c r="F3" s="108" t="s">
+        <v>87</v>
+      </c>
+      <c r="G3" s="117" t="s">
+        <v>44</v>
+      </c>
+      <c r="H3" s="116" t="s">
         <v>6</v>
       </c>
-      <c r="I3" s="122" t="s">
-        <v>84</v>
-      </c>
-      <c r="J3" s="121" t="s">
+      <c r="I3" s="123" t="s">
+        <v>78</v>
+      </c>
+      <c r="J3" s="122" t="s">
         <v>53</v>
       </c>
       <c r="L3" s="17"/>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A4" s="120"/>
-      <c r="B4" s="114"/>
-      <c r="C4" s="114"/>
-      <c r="D4" s="111"/>
-      <c r="E4" s="110"/>
-      <c r="F4" s="111"/>
-      <c r="G4" s="111"/>
-      <c r="H4" s="110"/>
-      <c r="I4" s="122"/>
-      <c r="J4" s="121"/>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A4" s="121"/>
+      <c r="B4" s="109"/>
+      <c r="C4" s="109"/>
+      <c r="D4" s="117"/>
+      <c r="E4" s="116"/>
+      <c r="F4" s="109"/>
+      <c r="G4" s="117"/>
+      <c r="H4" s="116"/>
+      <c r="I4" s="123"/>
+      <c r="J4" s="122"/>
       <c r="L4" s="17"/>
     </row>
-    <row r="5" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="98">
         <v>1</v>
       </c>
@@ -2855,32 +2821,33 @@
         <v>26</v>
       </c>
       <c r="D5" s="75">
-        <v>0</v>
+        <v>118177.84</v>
       </c>
       <c r="E5" s="75">
         <v>0</v>
       </c>
       <c r="F5" s="75">
-        <v>42383</v>
+        <f>D5-E5</f>
+        <v>118177.84</v>
       </c>
       <c r="G5" s="90">
-        <f>F5*1.48</f>
-        <v>62726.84</v>
+        <f>F5*3%</f>
+        <v>3545.3352</v>
       </c>
       <c r="H5" s="74">
         <v>0.121</v>
       </c>
       <c r="I5" s="75">
         <f>D$1*H5</f>
-        <v>13068</v>
+        <v>0</v>
       </c>
       <c r="J5" s="97">
-        <f>+F5+G5+I5</f>
-        <v>118177.84</v>
+        <f>+G5+I5+F5</f>
+        <v>121723.1752</v>
       </c>
       <c r="L5" s="17"/>
     </row>
-    <row r="6" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="98">
         <v>2</v>
       </c>
@@ -2891,32 +2858,33 @@
         <v>27</v>
       </c>
       <c r="D6" s="75">
-        <v>0</v>
+        <v>149494.16</v>
       </c>
       <c r="E6" s="75">
         <v>0</v>
       </c>
       <c r="F6" s="75">
-        <v>54967</v>
+        <f t="shared" ref="F6:F12" si="0">D6-E6</f>
+        <v>149494.16</v>
       </c>
       <c r="G6" s="90">
-        <f t="shared" ref="G6:G12" si="0">F6*1.48</f>
-        <v>81351.16</v>
+        <f t="shared" ref="G6:G12" si="1">F6*3%</f>
+        <v>4484.8248000000003</v>
       </c>
       <c r="H6" s="74">
         <v>0.122</v>
       </c>
       <c r="I6" s="75">
-        <f t="shared" ref="I6:I12" si="1">D$1*H6</f>
-        <v>13176</v>
+        <f>D$1*H6</f>
+        <v>0</v>
       </c>
       <c r="J6" s="97">
-        <f t="shared" ref="J6:J12" si="2">+F6+G6+I6</f>
-        <v>149494.16</v>
+        <f t="shared" ref="J6:J12" si="2">+G6+I6+F6</f>
+        <v>153978.98480000001</v>
       </c>
       <c r="L6" s="17"/>
     </row>
-    <row r="7" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="98">
         <v>3</v>
       </c>
@@ -2927,32 +2895,34 @@
         <v>28</v>
       </c>
       <c r="D7" s="75">
-        <v>0</v>
+        <v>12636</v>
       </c>
       <c r="E7" s="75">
-        <v>0</v>
+        <f>D7</f>
+        <v>12636</v>
       </c>
       <c r="F7" s="75">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G7" s="90">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="H7" s="74">
         <v>0.11700000000000001</v>
       </c>
       <c r="I7" s="75">
-        <f t="shared" si="1"/>
-        <v>12636</v>
+        <f>D$1*H7</f>
+        <v>0</v>
       </c>
       <c r="J7" s="97">
         <f t="shared" si="2"/>
-        <v>12636</v>
+        <v>0</v>
       </c>
       <c r="L7" s="17"/>
     </row>
-    <row r="8" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="98">
         <v>4</v>
       </c>
@@ -2963,32 +2933,33 @@
         <v>29</v>
       </c>
       <c r="D8" s="75">
-        <v>0</v>
+        <v>143366.72</v>
       </c>
       <c r="E8" s="75">
         <v>0</v>
       </c>
       <c r="F8" s="75">
-        <v>52714</v>
+        <f t="shared" si="0"/>
+        <v>143366.72</v>
       </c>
       <c r="G8" s="90">
-        <f t="shared" si="0"/>
-        <v>78016.72</v>
+        <f t="shared" si="1"/>
+        <v>4301.0015999999996</v>
       </c>
       <c r="H8" s="74">
         <v>0.11700000000000001</v>
       </c>
       <c r="I8" s="75">
-        <f t="shared" si="1"/>
-        <v>12636</v>
+        <f>D$1*H8</f>
+        <v>0</v>
       </c>
       <c r="J8" s="97">
         <f t="shared" si="2"/>
-        <v>143366.72</v>
+        <v>147667.72159999999</v>
       </c>
       <c r="L8" s="17"/>
     </row>
-    <row r="9" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="98">
         <v>5</v>
       </c>
@@ -2999,32 +2970,33 @@
         <v>26</v>
       </c>
       <c r="D9" s="75">
-        <v>0</v>
+        <v>133806.24000000002</v>
       </c>
       <c r="E9" s="75">
         <v>0</v>
       </c>
       <c r="F9" s="75">
-        <v>47988</v>
+        <f t="shared" si="0"/>
+        <v>133806.24000000002</v>
       </c>
       <c r="G9" s="90">
-        <f t="shared" si="0"/>
-        <v>71022.240000000005</v>
+        <f t="shared" si="1"/>
+        <v>4014.1872000000003</v>
       </c>
       <c r="H9" s="74">
         <v>0.13700000000000001</v>
       </c>
       <c r="I9" s="75">
-        <f t="shared" si="1"/>
-        <v>14796.000000000002</v>
+        <f>D$1*H9</f>
+        <v>0</v>
       </c>
       <c r="J9" s="97">
         <f t="shared" si="2"/>
-        <v>133806.24000000002</v>
+        <v>137820.42720000003</v>
       </c>
       <c r="L9" s="17"/>
     </row>
-    <row r="10" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="98">
         <v>6</v>
       </c>
@@ -3035,32 +3007,33 @@
         <v>26</v>
       </c>
       <c r="D10" s="75">
-        <v>0</v>
+        <v>128921.28</v>
       </c>
       <c r="E10" s="75">
         <v>0</v>
       </c>
       <c r="F10" s="75">
-        <v>46236</v>
+        <f t="shared" si="0"/>
+        <v>128921.28</v>
       </c>
       <c r="G10" s="90">
-        <f t="shared" si="0"/>
-        <v>68429.279999999999</v>
+        <f t="shared" si="1"/>
+        <v>3867.6383999999998</v>
       </c>
       <c r="H10" s="74">
         <v>0.13200000000000001</v>
       </c>
       <c r="I10" s="75">
-        <f t="shared" si="1"/>
-        <v>14256</v>
+        <f>D$1*H10</f>
+        <v>0</v>
       </c>
       <c r="J10" s="97">
         <f t="shared" si="2"/>
-        <v>128921.28</v>
+        <v>132788.9184</v>
       </c>
       <c r="L10" s="17"/>
     </row>
-    <row r="11" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="98">
         <v>7</v>
       </c>
@@ -3071,32 +3044,34 @@
         <v>28</v>
       </c>
       <c r="D11" s="75">
-        <v>0</v>
+        <v>13716</v>
       </c>
       <c r="E11" s="75">
-        <v>0</v>
+        <f>D11</f>
+        <v>13716</v>
       </c>
       <c r="F11" s="75">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G11" s="90">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="H11" s="74">
         <v>0.127</v>
       </c>
       <c r="I11" s="75">
-        <f t="shared" si="1"/>
-        <v>13716</v>
+        <f>D$1*H11</f>
+        <v>0</v>
       </c>
       <c r="J11" s="97">
         <f t="shared" si="2"/>
-        <v>13716</v>
+        <v>0</v>
       </c>
       <c r="L11" s="17"/>
     </row>
-    <row r="12" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="98">
         <v>8</v>
       </c>
@@ -3107,32 +3082,33 @@
         <v>30</v>
       </c>
       <c r="D12" s="75">
-        <v>0</v>
+        <v>13716</v>
       </c>
       <c r="E12" s="75">
         <v>0</v>
       </c>
       <c r="F12" s="75">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>13716</v>
       </c>
       <c r="G12" s="90">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>411.47999999999996</v>
       </c>
       <c r="H12" s="74">
         <v>0.127</v>
       </c>
       <c r="I12" s="75">
-        <f t="shared" si="1"/>
-        <v>13716</v>
+        <f>D$1*H12</f>
+        <v>0</v>
       </c>
       <c r="J12" s="97">
         <f t="shared" si="2"/>
-        <v>13716</v>
+        <v>14127.48</v>
       </c>
       <c r="L12" s="17"/>
     </row>
-    <row r="13" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="77" t="s">
         <v>10</v>
       </c>
@@ -3140,31 +3116,28 @@
       <c r="C13" s="79"/>
       <c r="D13" s="80">
         <f>SUM(D5:D12)</f>
-        <v>0</v>
+        <v>713834.24</v>
       </c>
       <c r="E13" s="80">
         <f>SUM(E5:E12)</f>
-        <v>0</v>
-      </c>
-      <c r="F13" s="80">
-        <f t="shared" ref="F13" si="3">SUM(F5:F12)</f>
-        <v>244288</v>
-      </c>
+        <v>26352</v>
+      </c>
+      <c r="F13" s="80"/>
       <c r="G13" s="80">
         <f>SUM(G5:G12)</f>
-        <v>361546.23999999999</v>
+        <v>20624.467199999999</v>
       </c>
       <c r="H13" s="70">
-        <f t="shared" ref="H13" si="4">SUM(H5:H12)</f>
+        <f t="shared" ref="H13" si="3">SUM(H5:H12)</f>
         <v>1</v>
       </c>
       <c r="I13" s="80">
         <f>SUM(I5:I12)</f>
-        <v>108000</v>
+        <v>0</v>
       </c>
       <c r="J13" s="81">
         <f>SUM(J5:J12)</f>
-        <v>713834.24</v>
+        <v>708106.70719999995</v>
       </c>
       <c r="L13" s="17"/>
     </row>

--- a/DRAGO/Noviembre/EXPENSAS-Noviembre.xlsx
+++ b/DRAGO/Noviembre/EXPENSAS-Noviembre.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\DRAGO\Noviembre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8111940-9741-4867-BB11-7629FE0943AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E1B08CC-58D6-4A09-952F-201ED50856C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="detalle y gastos" sheetId="3" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="extraordinarias" sheetId="4" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'detalle y gastos'!$A$1:$C$47</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'detalle y gastos'!$A$1:$C$48</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'prorrateo '!$A$1:$M$33</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="91">
   <si>
     <t>UF</t>
   </si>
@@ -283,9 +283,6 @@
     <t>Período NOVIEMBRE 2025</t>
   </si>
   <si>
-    <t>Recarga de matafuegos-  Matafuegos FIRE</t>
-  </si>
-  <si>
     <t>Colocacion de membarana en techo - A dos aguas - Material y mano de obra</t>
   </si>
   <si>
@@ -293,6 +290,15 @@
   </si>
   <si>
     <t>Ingresos extraordinarios</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jardineria - Servicios </t>
+  </si>
+  <si>
+    <t>Nicolas - Fumigacion 22/11</t>
+  </si>
+  <si>
+    <t>Articulos de limpieza</t>
   </si>
 </sst>
 </file>
@@ -832,7 +838,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="128">
+  <cellXfs count="127">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -996,6 +1002,9 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="25" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="11" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="11" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1053,10 +1062,6 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="16" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="11" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="11" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -1424,7 +1429,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:H56"/>
+  <dimension ref="A2:H57"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
@@ -1607,241 +1612,255 @@
       <c r="F24" s="18"/>
     </row>
     <row r="25" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A25" s="124" t="s">
-        <v>86</v>
+      <c r="A25" s="46" t="s">
+        <v>89</v>
       </c>
       <c r="B25" s="59"/>
       <c r="C25" s="51">
-        <v>180000</v>
+        <v>50000</v>
       </c>
       <c r="F25" s="18"/>
     </row>
     <row r="26" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" s="46" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="B26" s="59"/>
       <c r="C26" s="51">
-        <v>60899.97</v>
+        <v>32850</v>
       </c>
       <c r="F26" s="18"/>
     </row>
     <row r="27" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A27" s="46" t="s">
+      <c r="A27" s="105" t="s">
+        <v>88</v>
+      </c>
+      <c r="B27" s="59"/>
+      <c r="C27" s="51">
+        <v>90000</v>
+      </c>
+      <c r="F27" s="18"/>
+    </row>
+    <row r="28" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A28" s="46" t="s">
         <v>68</v>
       </c>
-      <c r="B27" s="56"/>
-      <c r="C27" s="52"/>
-      <c r="D27" s="5"/>
-      <c r="E27" s="12"/>
-      <c r="F27" s="18"/>
-    </row>
-    <row r="28" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A28" s="57"/>
-      <c r="B28" s="58"/>
-      <c r="C28" s="42">
-        <f>SUM(C23:C27)</f>
-        <v>312782.96999999997</v>
-      </c>
+      <c r="B28" s="56"/>
+      <c r="C28" s="52"/>
+      <c r="D28" s="5"/>
+      <c r="E28" s="12"/>
       <c r="F28" s="18"/>
     </row>
     <row r="29" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A29" s="49" t="s">
+      <c r="A29" s="57"/>
+      <c r="B29" s="58"/>
+      <c r="C29" s="42">
+        <f>SUM(C23:C28)</f>
+        <v>244733</v>
+      </c>
+      <c r="F29" s="18"/>
+    </row>
+    <row r="30" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A30" s="49" t="s">
         <v>67</v>
       </c>
-      <c r="B29" s="49"/>
-      <c r="C29" s="60">
-        <f>+C28+C22</f>
-        <v>598209.54</v>
-      </c>
-      <c r="F29" s="18"/>
-    </row>
-    <row r="30" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C30" s="43"/>
+      <c r="B30" s="49"/>
+      <c r="C30" s="60">
+        <f>+C29+C22</f>
+        <v>530159.57000000007</v>
+      </c>
       <c r="F30" s="18"/>
     </row>
     <row r="31" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A31" s="19" t="s">
-        <v>43</v>
-      </c>
       <c r="C31" s="43"/>
       <c r="F31" s="18"/>
     </row>
     <row r="32" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A32" s="105"/>
-      <c r="B32" s="106"/>
-      <c r="C32" s="101"/>
+      <c r="A32" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="C32" s="43"/>
       <c r="F32" s="18"/>
     </row>
     <row r="33" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A33" s="46"/>
-      <c r="B33" s="46"/>
-      <c r="C33" s="52"/>
+      <c r="A33" s="108"/>
+      <c r="B33" s="109"/>
+      <c r="C33" s="101"/>
       <c r="F33" s="18"/>
     </row>
     <row r="34" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A34" s="46"/>
+      <c r="A34" s="105" t="s">
+        <v>85</v>
+      </c>
       <c r="B34" s="46"/>
-      <c r="C34" s="52"/>
+      <c r="C34" s="51">
+        <v>180000</v>
+      </c>
       <c r="F34" s="18"/>
     </row>
     <row r="35" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C35" s="44"/>
+      <c r="A35" s="46"/>
+      <c r="B35" s="46"/>
+      <c r="C35" s="52"/>
       <c r="F35" s="18"/>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="19" t="s">
+    <row r="36" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="C36" s="44"/>
+      <c r="F36" s="18"/>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="B36" s="19"/>
-      <c r="C36" s="20">
-        <f>+C32+C33+C34+C35</f>
-        <v>0</v>
-      </c>
-      <c r="E36" s="12"/>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="29" t="s">
+      <c r="B37" s="19"/>
+      <c r="C37" s="20">
+        <f>SUM(C33:C36)</f>
+        <v>180000</v>
+      </c>
+      <c r="E37" s="12"/>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="B38" s="29"/>
-      <c r="C38" s="30">
-        <f>+C36+C29</f>
-        <v>598209.54</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="5" t="s">
+      <c r="B39" s="29"/>
+      <c r="C39" s="30">
+        <f>+C37+C30</f>
+        <v>710159.57000000007</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="5" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="31" t="s">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="B41" s="28"/>
-      <c r="C41" s="33">
+      <c r="B42" s="28"/>
+      <c r="C42" s="33">
         <v>66868.53562338918</v>
       </c>
-      <c r="D41" s="6"/>
-      <c r="E41" s="6"/>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>8</v>
-      </c>
-      <c r="C42" s="27">
-        <f>'prorrateo '!F13</f>
-        <v>419434.17550000001</v>
-      </c>
-      <c r="D42" s="12"/>
-      <c r="E42" s="12"/>
+      <c r="D42" s="6"/>
+      <c r="E42" s="6"/>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>88</v>
-      </c>
-      <c r="C43" s="126">
+        <v>8</v>
+      </c>
+      <c r="C43" s="27">
+        <f>'prorrateo '!F13</f>
+        <v>425923.61005000002</v>
+      </c>
+      <c r="D43" s="12"/>
+      <c r="E43" s="12"/>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>87</v>
+      </c>
+      <c r="C44" s="106">
         <f>extraordinarias!E13</f>
         <v>26352</v>
       </c>
-      <c r="D43" s="12"/>
-      <c r="E43" s="12"/>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>75</v>
-      </c>
-      <c r="C44" s="61">
-        <f>-C36</f>
-        <v>0</v>
-      </c>
       <c r="D44" s="12"/>
       <c r="E44" s="12"/>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
+        <v>75</v>
+      </c>
+      <c r="C45" s="61">
+        <f>-C37</f>
+        <v>-180000</v>
+      </c>
+      <c r="D45" s="12"/>
+      <c r="E45" s="12"/>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
         <v>66</v>
       </c>
-      <c r="C45" s="61">
-        <f>-(C29-C27)</f>
-        <v>-598209.54</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A46" s="31" t="s">
+      <c r="C46" s="61">
+        <f>-(C30-C28)</f>
+        <v>-530159.57000000007</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" s="31" t="s">
         <v>15</v>
       </c>
-      <c r="B46" s="28"/>
-      <c r="C46" s="33">
-        <f>SUM(C41:C45)</f>
-        <v>-85554.828876610845</v>
-      </c>
-      <c r="D46" s="6"/>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A47" s="15"/>
-      <c r="B47" s="14"/>
-      <c r="C47" s="16"/>
+      <c r="B47" s="28"/>
+      <c r="C47" s="33">
+        <f>SUM(C42:C46)</f>
+        <v>-191015.42432661087</v>
+      </c>
+      <c r="D47" s="6"/>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="15"/>
       <c r="B48" s="14"/>
       <c r="C48" s="16"/>
-      <c r="F48" s="62"/>
-    </row>
-    <row r="49" spans="1:3" ht="2.25" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="15"/>
       <c r="B49" s="14"/>
       <c r="C49" s="16"/>
-    </row>
-    <row r="50" spans="1:3" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="45" t="s">
+      <c r="F49" s="62"/>
+    </row>
+    <row r="50" spans="1:6" ht="2.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="15"/>
+      <c r="B50" s="14"/>
+      <c r="C50" s="16"/>
+    </row>
+    <row r="51" spans="1:6" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="45" t="s">
         <v>60</v>
       </c>
-      <c r="B50" s="64"/>
-      <c r="C50" s="65">
+      <c r="B51" s="64"/>
+      <c r="C51" s="65">
         <v>109834.99657000002</v>
       </c>
     </row>
-    <row r="51" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="46"/>
-      <c r="B51" s="46"/>
-      <c r="C51" s="50"/>
-    </row>
-    <row r="52" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="49" t="s">
+    <row r="52" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="46"/>
+      <c r="B52" s="46"/>
+      <c r="C52" s="50"/>
+    </row>
+    <row r="53" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="49" t="s">
         <v>4</v>
       </c>
-      <c r="B52" s="47"/>
-      <c r="C52" s="48">
-        <f>SUM(C50:C51)</f>
+      <c r="B53" s="47"/>
+      <c r="C53" s="48">
+        <f>SUM(C51:C52)</f>
         <v>109834.99657000002</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A53" s="14"/>
-      <c r="B53" s="14"/>
-      <c r="C53" s="14"/>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="14"/>
       <c r="B54" s="14"/>
       <c r="C54" s="14"/>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="14"/>
       <c r="B55" s="14"/>
       <c r="C55" s="14"/>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="14"/>
       <c r="B56" s="14"/>
       <c r="C56" s="14"/>
     </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A57" s="14"/>
+      <c r="B57" s="14"/>
+      <c r="C57" s="14"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="A33:B33"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="B4" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
@@ -1881,7 +1900,7 @@
         <v>47</v>
       </c>
       <c r="E1" s="103">
-        <v>598209.54</v>
+        <v>530159.57000000007</v>
       </c>
       <c r="G1" t="str">
         <f>'detalle y gastos'!C7</f>
@@ -1909,58 +1928,58 @@
       <c r="M2" s="67"/>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A3" s="110"/>
-      <c r="B3" s="108" t="s">
+      <c r="A3" s="113"/>
+      <c r="B3" s="111" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="116" t="s">
+      <c r="C3" s="119" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="117" t="s">
+      <c r="D3" s="120" t="s">
         <v>54</v>
       </c>
-      <c r="E3" s="108" t="s">
+      <c r="E3" s="111" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="114" t="s">
+      <c r="F3" s="117" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="116" t="s">
+      <c r="G3" s="119" t="s">
         <v>52</v>
       </c>
-      <c r="H3" s="114" t="s">
+      <c r="H3" s="117" t="s">
         <v>44</v>
       </c>
-      <c r="I3" s="116" t="s">
+      <c r="I3" s="119" t="s">
         <v>6</v>
       </c>
-      <c r="J3" s="118" t="s">
+      <c r="J3" s="121" t="s">
         <v>80</v>
       </c>
-      <c r="K3" s="112" t="s">
+      <c r="K3" s="115" t="s">
         <v>69</v>
       </c>
-      <c r="L3" s="112" t="s">
+      <c r="L3" s="115" t="s">
         <v>70</v>
       </c>
-      <c r="M3" s="112" t="s">
+      <c r="M3" s="115" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A4" s="111"/>
-      <c r="B4" s="109"/>
-      <c r="C4" s="116"/>
-      <c r="D4" s="117"/>
-      <c r="E4" s="109"/>
-      <c r="F4" s="115"/>
-      <c r="G4" s="116"/>
-      <c r="H4" s="115"/>
-      <c r="I4" s="116"/>
-      <c r="J4" s="118"/>
-      <c r="K4" s="113"/>
-      <c r="L4" s="113"/>
-      <c r="M4" s="113"/>
+      <c r="A4" s="114"/>
+      <c r="B4" s="112"/>
+      <c r="C4" s="119"/>
+      <c r="D4" s="120"/>
+      <c r="E4" s="112"/>
+      <c r="F4" s="118"/>
+      <c r="G4" s="119"/>
+      <c r="H4" s="118"/>
+      <c r="I4" s="119"/>
+      <c r="J4" s="121"/>
+      <c r="K4" s="116"/>
+      <c r="L4" s="116"/>
+      <c r="M4" s="116"/>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" s="68">
@@ -1978,7 +1997,7 @@
       <c r="E5" s="37">
         <v>52345.718659999991</v>
       </c>
-      <c r="F5" s="125">
+      <c r="F5" s="85">
         <v>52350</v>
       </c>
       <c r="G5" s="37">
@@ -1995,15 +2014,15 @@
       <c r="J5" s="63"/>
       <c r="K5" s="75">
         <f>E1*I5</f>
-        <v>72383.354340000005</v>
+        <v>64149.307970000009</v>
       </c>
       <c r="L5" s="75">
         <f>E5-F5+H5+K5+J5</f>
-        <v>72379.073000000004</v>
+        <v>64145.02663</v>
       </c>
       <c r="M5" s="76">
         <f>L5+L5*4%</f>
-        <v>75274.235920000006</v>
+        <v>66710.827695200001</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
@@ -2022,7 +2041,7 @@
       <c r="E6" s="37">
         <v>52780.719699999994</v>
       </c>
-      <c r="F6" s="125">
+      <c r="F6" s="85">
         <f t="shared" ref="F6:F11" si="0">E6</f>
         <v>52780.719699999994</v>
       </c>
@@ -2040,15 +2059,15 @@
       <c r="J6" s="63"/>
       <c r="K6" s="75">
         <f>E1*I6</f>
-        <v>72981.563880000002</v>
+        <v>64679.467540000005</v>
       </c>
       <c r="L6" s="75">
         <f t="shared" ref="L6:L12" si="3">E6-F6+H6+K6+J6</f>
-        <v>72981.563880000002</v>
+        <v>64679.467540000005</v>
       </c>
       <c r="M6" s="76">
         <f t="shared" ref="M6:M12" si="4">L6+L6*4%</f>
-        <v>75900.826435199997</v>
+        <v>67266.646241599999</v>
       </c>
       <c r="O6" s="83"/>
       <c r="Q6" s="82"/>
@@ -2069,7 +2088,7 @@
       <c r="E7" s="37">
         <v>50617.575449999997</v>
       </c>
-      <c r="F7" s="125">
+      <c r="F7" s="85">
         <v>94528</v>
       </c>
       <c r="G7" s="37">
@@ -2086,15 +2105,15 @@
       <c r="J7" s="63"/>
       <c r="K7" s="75">
         <f>E1*I7</f>
-        <v>69990.516180000006</v>
+        <v>62028.66969000001</v>
       </c>
       <c r="L7" s="75">
         <f t="shared" si="3"/>
-        <v>26080.091630000003</v>
+        <v>18118.245140000006</v>
       </c>
       <c r="M7" s="76">
         <f t="shared" si="4"/>
-        <v>27123.295295200001</v>
+        <v>18842.974945600006</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
@@ -2113,17 +2132,14 @@
       <c r="E8" s="85">
         <v>50617.575449999997</v>
       </c>
-      <c r="F8" s="127">
-        <f>E8</f>
-        <v>50617.575449999997</v>
-      </c>
+      <c r="F8" s="107"/>
       <c r="G8" s="37">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>50617.575449999997</v>
       </c>
       <c r="H8" s="37">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1518.5272634999999</v>
       </c>
       <c r="I8" s="74">
         <v>0.11700000000000001</v>
@@ -2131,15 +2147,15 @@
       <c r="J8" s="63"/>
       <c r="K8" s="75">
         <f>E1*I8</f>
-        <v>69990.516180000006</v>
+        <v>62028.66969000001</v>
       </c>
       <c r="L8" s="75">
         <f t="shared" si="3"/>
-        <v>69990.516180000006</v>
+        <v>114164.77240350001</v>
       </c>
       <c r="M8" s="76">
         <f t="shared" si="4"/>
-        <v>72790.136827200011</v>
+        <v>118731.36329964001</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
@@ -2158,7 +2174,7 @@
       <c r="E9" s="37">
         <v>59270.152450000001</v>
       </c>
-      <c r="F9" s="125">
+      <c r="F9" s="85">
         <f>E9</f>
         <v>59270.152450000001</v>
       </c>
@@ -2176,15 +2192,15 @@
       <c r="J9" s="63"/>
       <c r="K9" s="75">
         <f>E1*I9</f>
-        <v>81954.706980000017</v>
+        <v>72631.86109000002</v>
       </c>
       <c r="L9" s="75">
         <f t="shared" si="3"/>
-        <v>81954.706980000017</v>
+        <v>72631.86109000002</v>
       </c>
       <c r="M9" s="76">
         <f t="shared" si="4"/>
-        <v>85232.895259200013</v>
+        <v>75537.135533600027</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -2201,16 +2217,18 @@
         <v>77</v>
       </c>
       <c r="E10" s="37">
-        <v>179714.93211211998</v>
-      </c>
-      <c r="F10" s="85"/>
+        <v>186903.52939660478</v>
+      </c>
+      <c r="F10" s="85">
+        <v>57107.01</v>
+      </c>
       <c r="G10" s="37">
         <f t="shared" si="1"/>
-        <v>179714.93211211998</v>
+        <v>129796.51939660477</v>
       </c>
       <c r="H10" s="37">
         <f t="shared" si="2"/>
-        <v>5391.4479633635992</v>
+        <v>3893.8955818981431</v>
       </c>
       <c r="I10" s="74">
         <v>0.13200000000000001</v>
@@ -2218,15 +2236,15 @@
       <c r="J10" s="63"/>
       <c r="K10" s="75">
         <f>E1*I10</f>
-        <v>78963.659280000007</v>
+        <v>69981.063240000018</v>
       </c>
       <c r="L10" s="75">
         <f t="shared" si="3"/>
-        <v>264070.0393554836</v>
+        <v>203671.47821850292</v>
       </c>
       <c r="M10" s="76">
         <f t="shared" si="4"/>
-        <v>274632.84092970297</v>
+        <v>211818.33734724304</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
@@ -2245,7 +2263,7 @@
       <c r="E11" s="37">
         <v>54943.863949999999</v>
       </c>
-      <c r="F11" s="125">
+      <c r="F11" s="85">
         <f t="shared" si="0"/>
         <v>54943.863949999999</v>
       </c>
@@ -2263,15 +2281,15 @@
       <c r="J11" s="63"/>
       <c r="K11" s="75">
         <f>E1*I11</f>
-        <v>75972.611580000012</v>
+        <v>67330.265390000015</v>
       </c>
       <c r="L11" s="75">
         <f t="shared" si="3"/>
-        <v>75972.611580000012</v>
+        <v>67330.265390000015</v>
       </c>
       <c r="M11" s="76">
         <f t="shared" si="4"/>
-        <v>79011.516043200012</v>
+        <v>70023.476005600009</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
@@ -2290,7 +2308,7 @@
       <c r="E12" s="37">
         <v>54943.863949999999</v>
       </c>
-      <c r="F12" s="125">
+      <c r="F12" s="85">
         <f>E12</f>
         <v>54943.863949999999</v>
       </c>
@@ -2308,15 +2326,15 @@
       <c r="J12" s="63"/>
       <c r="K12" s="75">
         <f>E1*I12</f>
-        <v>75972.611580000012</v>
+        <v>67330.265390000015</v>
       </c>
       <c r="L12" s="75">
         <f t="shared" si="3"/>
-        <v>75972.611580000012</v>
+        <v>67330.265390000015</v>
       </c>
       <c r="M12" s="76">
         <f t="shared" si="4"/>
-        <v>79011.516043200012</v>
+        <v>70023.476005600009</v>
       </c>
     </row>
     <row r="13" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2328,16 +2346,16 @@
       <c r="D13" s="79"/>
       <c r="E13" s="80">
         <f>SUM(E5:E12)</f>
-        <v>555234.40172212</v>
+        <v>562422.99900660478</v>
       </c>
       <c r="F13" s="69">
         <f>SUM(F5:F12)</f>
-        <v>419434.17550000001</v>
+        <v>425923.61005000002</v>
       </c>
       <c r="G13" s="69"/>
       <c r="H13" s="69">
         <f>SUM(H5:H12)</f>
-        <v>5391.4479633635992</v>
+        <v>5412.4228453981432</v>
       </c>
       <c r="I13" s="70">
         <f t="shared" ref="I13" si="5">SUM(I5:I12)</f>
@@ -2349,61 +2367,61 @@
       </c>
       <c r="K13" s="80">
         <f>SUM(K5:K12)</f>
-        <v>598209.54</v>
+        <v>530159.57000000007</v>
       </c>
       <c r="L13" s="80">
         <f>SUM(L5:L12)</f>
-        <v>739401.21418548375</v>
+        <v>672071.38180200313</v>
       </c>
       <c r="M13" s="81">
         <f>SUM(M5:M12)</f>
-        <v>768977.26275290304</v>
+        <v>698954.23707408318</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="C15" s="107" t="s">
+      <c r="C15" s="110" t="s">
         <v>81</v>
       </c>
-      <c r="D15" s="107"/>
-      <c r="E15" s="107"/>
-      <c r="F15" s="107"/>
-      <c r="G15" s="107"/>
-      <c r="H15" s="107"/>
-      <c r="I15" s="107"/>
-      <c r="J15" s="107"/>
-      <c r="K15" s="107"/>
-      <c r="L15" s="107"/>
+      <c r="D15" s="110"/>
+      <c r="E15" s="110"/>
+      <c r="F15" s="110"/>
+      <c r="G15" s="110"/>
+      <c r="H15" s="110"/>
+      <c r="I15" s="110"/>
+      <c r="J15" s="110"/>
+      <c r="K15" s="110"/>
+      <c r="L15" s="110"/>
     </row>
     <row r="16" spans="1:17" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="40" t="s">
         <v>48</v>
       </c>
-      <c r="C16" s="107"/>
-      <c r="D16" s="107"/>
-      <c r="E16" s="107"/>
-      <c r="F16" s="107"/>
-      <c r="G16" s="107"/>
-      <c r="H16" s="107"/>
-      <c r="I16" s="107"/>
-      <c r="J16" s="107"/>
-      <c r="K16" s="107"/>
-      <c r="L16" s="107"/>
+      <c r="C16" s="110"/>
+      <c r="D16" s="110"/>
+      <c r="E16" s="110"/>
+      <c r="F16" s="110"/>
+      <c r="G16" s="110"/>
+      <c r="H16" s="110"/>
+      <c r="I16" s="110"/>
+      <c r="J16" s="110"/>
+      <c r="K16" s="110"/>
+      <c r="L16" s="110"/>
     </row>
     <row r="17" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="24" t="s">
         <v>50</v>
       </c>
       <c r="B17" s="25"/>
-      <c r="C17" s="107"/>
-      <c r="D17" s="107"/>
-      <c r="E17" s="107"/>
-      <c r="F17" s="107"/>
-      <c r="G17" s="107"/>
-      <c r="H17" s="107"/>
-      <c r="I17" s="107"/>
-      <c r="J17" s="107"/>
-      <c r="K17" s="107"/>
-      <c r="L17" s="107"/>
+      <c r="C17" s="110"/>
+      <c r="D17" s="110"/>
+      <c r="E17" s="110"/>
+      <c r="F17" s="110"/>
+      <c r="G17" s="110"/>
+      <c r="H17" s="110"/>
+      <c r="I17" s="110"/>
+      <c r="J17" s="110"/>
+      <c r="K17" s="110"/>
+      <c r="L17" s="110"/>
       <c r="M17" s="26"/>
     </row>
     <row r="18" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
@@ -2413,16 +2431,16 @@
       <c r="B18" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C18" s="107"/>
-      <c r="D18" s="107"/>
-      <c r="E18" s="107"/>
-      <c r="F18" s="107"/>
-      <c r="G18" s="107"/>
-      <c r="H18" s="107"/>
-      <c r="I18" s="107"/>
-      <c r="J18" s="107"/>
-      <c r="K18" s="107"/>
-      <c r="L18" s="107"/>
+      <c r="C18" s="110"/>
+      <c r="D18" s="110"/>
+      <c r="E18" s="110"/>
+      <c r="F18" s="110"/>
+      <c r="G18" s="110"/>
+      <c r="H18" s="110"/>
+      <c r="I18" s="110"/>
+      <c r="J18" s="110"/>
+      <c r="K18" s="110"/>
+      <c r="L18" s="110"/>
       <c r="M18" s="36" t="s">
         <v>4</v>
       </c>
@@ -2430,16 +2448,16 @@
     <row r="19" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2"/>
       <c r="B19" s="7"/>
-      <c r="C19" s="107"/>
-      <c r="D19" s="107"/>
-      <c r="E19" s="107"/>
-      <c r="F19" s="107"/>
-      <c r="G19" s="107"/>
-      <c r="H19" s="107"/>
-      <c r="I19" s="107"/>
-      <c r="J19" s="107"/>
-      <c r="K19" s="107"/>
-      <c r="L19" s="107"/>
+      <c r="C19" s="110"/>
+      <c r="D19" s="110"/>
+      <c r="E19" s="110"/>
+      <c r="F19" s="110"/>
+      <c r="G19" s="110"/>
+      <c r="H19" s="110"/>
+      <c r="I19" s="110"/>
+      <c r="J19" s="110"/>
+      <c r="K19" s="110"/>
+      <c r="L19" s="110"/>
       <c r="M19" s="32" t="s">
         <v>5</v>
       </c>
@@ -2451,16 +2469,16 @@
       <c r="B20" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="C20" s="107"/>
-      <c r="D20" s="107"/>
-      <c r="E20" s="107"/>
-      <c r="F20" s="107"/>
-      <c r="G20" s="107"/>
-      <c r="H20" s="107"/>
-      <c r="I20" s="107"/>
-      <c r="J20" s="107"/>
-      <c r="K20" s="107"/>
-      <c r="L20" s="107"/>
+      <c r="C20" s="110"/>
+      <c r="D20" s="110"/>
+      <c r="E20" s="110"/>
+      <c r="F20" s="110"/>
+      <c r="G20" s="110"/>
+      <c r="H20" s="110"/>
+      <c r="I20" s="110"/>
+      <c r="J20" s="110"/>
+      <c r="K20" s="110"/>
+      <c r="L20" s="110"/>
       <c r="M20" s="34" t="e">
         <f>+#REF!+H20+K20</f>
         <v>#REF!</v>
@@ -2473,16 +2491,16 @@
       <c r="B21" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="C21" s="107"/>
-      <c r="D21" s="107"/>
-      <c r="E21" s="107"/>
-      <c r="F21" s="107"/>
-      <c r="G21" s="107"/>
-      <c r="H21" s="107"/>
-      <c r="I21" s="107"/>
-      <c r="J21" s="107"/>
-      <c r="K21" s="107"/>
-      <c r="L21" s="107"/>
+      <c r="C21" s="110"/>
+      <c r="D21" s="110"/>
+      <c r="E21" s="110"/>
+      <c r="F21" s="110"/>
+      <c r="G21" s="110"/>
+      <c r="H21" s="110"/>
+      <c r="I21" s="110"/>
+      <c r="J21" s="110"/>
+      <c r="K21" s="110"/>
+      <c r="L21" s="110"/>
       <c r="M21" s="34" t="e">
         <f>+#REF!+H21+K21</f>
         <v>#REF!</v>
@@ -2495,16 +2513,16 @@
       <c r="B22" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="C22" s="107"/>
-      <c r="D22" s="107"/>
-      <c r="E22" s="107"/>
-      <c r="F22" s="107"/>
-      <c r="G22" s="107"/>
-      <c r="H22" s="107"/>
-      <c r="I22" s="107"/>
-      <c r="J22" s="107"/>
-      <c r="K22" s="107"/>
-      <c r="L22" s="107"/>
+      <c r="C22" s="110"/>
+      <c r="D22" s="110"/>
+      <c r="E22" s="110"/>
+      <c r="F22" s="110"/>
+      <c r="G22" s="110"/>
+      <c r="H22" s="110"/>
+      <c r="I22" s="110"/>
+      <c r="J22" s="110"/>
+      <c r="K22" s="110"/>
+      <c r="L22" s="110"/>
       <c r="M22" s="34" t="e">
         <f>+#REF!+H22+K22</f>
         <v>#REF!</v>
@@ -2517,16 +2535,16 @@
       <c r="B23" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="C23" s="107"/>
-      <c r="D23" s="107"/>
-      <c r="E23" s="107"/>
-      <c r="F23" s="107"/>
-      <c r="G23" s="107"/>
-      <c r="H23" s="107"/>
-      <c r="I23" s="107"/>
-      <c r="J23" s="107"/>
-      <c r="K23" s="107"/>
-      <c r="L23" s="107"/>
+      <c r="C23" s="110"/>
+      <c r="D23" s="110"/>
+      <c r="E23" s="110"/>
+      <c r="F23" s="110"/>
+      <c r="G23" s="110"/>
+      <c r="H23" s="110"/>
+      <c r="I23" s="110"/>
+      <c r="J23" s="110"/>
+      <c r="K23" s="110"/>
+      <c r="L23" s="110"/>
       <c r="M23" s="34" t="e">
         <f>+#REF!+H23+K23</f>
         <v>#REF!</v>
@@ -2539,16 +2557,16 @@
       <c r="B24" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="C24" s="107"/>
-      <c r="D24" s="107"/>
-      <c r="E24" s="107"/>
-      <c r="F24" s="107"/>
-      <c r="G24" s="107"/>
-      <c r="H24" s="107"/>
-      <c r="I24" s="107"/>
-      <c r="J24" s="107"/>
-      <c r="K24" s="107"/>
-      <c r="L24" s="107"/>
+      <c r="C24" s="110"/>
+      <c r="D24" s="110"/>
+      <c r="E24" s="110"/>
+      <c r="F24" s="110"/>
+      <c r="G24" s="110"/>
+      <c r="H24" s="110"/>
+      <c r="I24" s="110"/>
+      <c r="J24" s="110"/>
+      <c r="K24" s="110"/>
+      <c r="L24" s="110"/>
       <c r="M24" s="34" t="e">
         <f>+#REF!+H24+K24</f>
         <v>#REF!</v>
@@ -2561,16 +2579,16 @@
       <c r="B25" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="C25" s="107"/>
-      <c r="D25" s="107"/>
-      <c r="E25" s="107"/>
-      <c r="F25" s="107"/>
-      <c r="G25" s="107"/>
-      <c r="H25" s="107"/>
-      <c r="I25" s="107"/>
-      <c r="J25" s="107"/>
-      <c r="K25" s="107"/>
-      <c r="L25" s="107"/>
+      <c r="C25" s="110"/>
+      <c r="D25" s="110"/>
+      <c r="E25" s="110"/>
+      <c r="F25" s="110"/>
+      <c r="G25" s="110"/>
+      <c r="H25" s="110"/>
+      <c r="I25" s="110"/>
+      <c r="J25" s="110"/>
+      <c r="K25" s="110"/>
+      <c r="L25" s="110"/>
       <c r="M25" s="34" t="e">
         <f>+#REF!+H25+K25</f>
         <v>#REF!</v>
@@ -2583,16 +2601,16 @@
       <c r="B26" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="C26" s="107"/>
-      <c r="D26" s="107"/>
-      <c r="E26" s="107"/>
-      <c r="F26" s="107"/>
-      <c r="G26" s="107"/>
-      <c r="H26" s="107"/>
-      <c r="I26" s="107"/>
-      <c r="J26" s="107"/>
-      <c r="K26" s="107"/>
-      <c r="L26" s="107"/>
+      <c r="C26" s="110"/>
+      <c r="D26" s="110"/>
+      <c r="E26" s="110"/>
+      <c r="F26" s="110"/>
+      <c r="G26" s="110"/>
+      <c r="H26" s="110"/>
+      <c r="I26" s="110"/>
+      <c r="J26" s="110"/>
+      <c r="K26" s="110"/>
+      <c r="L26" s="110"/>
       <c r="M26" s="34" t="e">
         <f>+#REF!+H26+K26</f>
         <v>#REF!</v>
@@ -2605,16 +2623,16 @@
       <c r="B27" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="C27" s="107"/>
-      <c r="D27" s="107"/>
-      <c r="E27" s="107"/>
-      <c r="F27" s="107"/>
-      <c r="G27" s="107"/>
-      <c r="H27" s="107"/>
-      <c r="I27" s="107"/>
-      <c r="J27" s="107"/>
-      <c r="K27" s="107"/>
-      <c r="L27" s="107"/>
+      <c r="C27" s="110"/>
+      <c r="D27" s="110"/>
+      <c r="E27" s="110"/>
+      <c r="F27" s="110"/>
+      <c r="G27" s="110"/>
+      <c r="H27" s="110"/>
+      <c r="I27" s="110"/>
+      <c r="J27" s="110"/>
+      <c r="K27" s="110"/>
+      <c r="L27" s="110"/>
       <c r="M27" s="34" t="e">
         <f>+#REF!+H27+K27</f>
         <v>#REF!</v>
@@ -2625,68 +2643,68 @@
         <v>10</v>
       </c>
       <c r="B28" s="9"/>
-      <c r="C28" s="107"/>
-      <c r="D28" s="107"/>
-      <c r="E28" s="107"/>
-      <c r="F28" s="107"/>
-      <c r="G28" s="107"/>
-      <c r="H28" s="107"/>
-      <c r="I28" s="107"/>
-      <c r="J28" s="107"/>
-      <c r="K28" s="107"/>
-      <c r="L28" s="107"/>
+      <c r="C28" s="110"/>
+      <c r="D28" s="110"/>
+      <c r="E28" s="110"/>
+      <c r="F28" s="110"/>
+      <c r="G28" s="110"/>
+      <c r="H28" s="110"/>
+      <c r="I28" s="110"/>
+      <c r="J28" s="110"/>
+      <c r="K28" s="110"/>
+      <c r="L28" s="110"/>
       <c r="M28" s="35" t="e">
         <f>SUM(M20:M27)</f>
         <v>#REF!</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="C29" s="107"/>
-      <c r="D29" s="107"/>
-      <c r="E29" s="107"/>
-      <c r="F29" s="107"/>
-      <c r="G29" s="107"/>
-      <c r="H29" s="107"/>
-      <c r="I29" s="107"/>
-      <c r="J29" s="107"/>
-      <c r="K29" s="107"/>
-      <c r="L29" s="107"/>
+      <c r="C29" s="110"/>
+      <c r="D29" s="110"/>
+      <c r="E29" s="110"/>
+      <c r="F29" s="110"/>
+      <c r="G29" s="110"/>
+      <c r="H29" s="110"/>
+      <c r="I29" s="110"/>
+      <c r="J29" s="110"/>
+      <c r="K29" s="110"/>
+      <c r="L29" s="110"/>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="C30" s="107"/>
-      <c r="D30" s="107"/>
-      <c r="E30" s="107"/>
-      <c r="F30" s="107"/>
-      <c r="G30" s="107"/>
-      <c r="H30" s="107"/>
-      <c r="I30" s="107"/>
-      <c r="J30" s="107"/>
-      <c r="K30" s="107"/>
-      <c r="L30" s="107"/>
+      <c r="C30" s="110"/>
+      <c r="D30" s="110"/>
+      <c r="E30" s="110"/>
+      <c r="F30" s="110"/>
+      <c r="G30" s="110"/>
+      <c r="H30" s="110"/>
+      <c r="I30" s="110"/>
+      <c r="J30" s="110"/>
+      <c r="K30" s="110"/>
+      <c r="L30" s="110"/>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="C31" s="107"/>
-      <c r="D31" s="107"/>
-      <c r="E31" s="107"/>
-      <c r="F31" s="107"/>
-      <c r="G31" s="107"/>
-      <c r="H31" s="107"/>
-      <c r="I31" s="107"/>
-      <c r="J31" s="107"/>
-      <c r="K31" s="107"/>
-      <c r="L31" s="107"/>
+      <c r="C31" s="110"/>
+      <c r="D31" s="110"/>
+      <c r="E31" s="110"/>
+      <c r="F31" s="110"/>
+      <c r="G31" s="110"/>
+      <c r="H31" s="110"/>
+      <c r="I31" s="110"/>
+      <c r="J31" s="110"/>
+      <c r="K31" s="110"/>
+      <c r="L31" s="110"/>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="C32" s="107"/>
-      <c r="D32" s="107"/>
-      <c r="E32" s="107"/>
-      <c r="F32" s="107"/>
-      <c r="G32" s="107"/>
-      <c r="H32" s="107"/>
-      <c r="I32" s="107"/>
-      <c r="J32" s="107"/>
-      <c r="K32" s="107"/>
-      <c r="L32" s="107"/>
+      <c r="C32" s="110"/>
+      <c r="D32" s="110"/>
+      <c r="E32" s="110"/>
+      <c r="F32" s="110"/>
+      <c r="G32" s="110"/>
+      <c r="H32" s="110"/>
+      <c r="I32" s="110"/>
+      <c r="J32" s="110"/>
+      <c r="K32" s="110"/>
+      <c r="L32" s="110"/>
     </row>
     <row r="39" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E39" s="39"/>
@@ -2736,10 +2754,10 @@
       </c>
       <c r="B1" s="92"/>
       <c r="C1" s="93"/>
-      <c r="D1" s="119">
-        <v>0</v>
-      </c>
-      <c r="E1" s="119"/>
+      <c r="D1" s="122">
+        <v>0</v>
+      </c>
+      <c r="E1" s="122"/>
       <c r="F1" s="104"/>
       <c r="G1" s="93"/>
       <c r="H1" s="93"/>
@@ -2765,49 +2783,49 @@
       <c r="L2" s="17"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="120" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="108" t="s">
+      <c r="A3" s="123" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="111" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="108" t="s">
+      <c r="C3" s="111" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="117" t="s">
+      <c r="D3" s="120" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="116" t="s">
+      <c r="E3" s="119" t="s">
         <v>51</v>
       </c>
-      <c r="F3" s="108" t="s">
-        <v>87</v>
-      </c>
-      <c r="G3" s="117" t="s">
+      <c r="F3" s="111" t="s">
+        <v>86</v>
+      </c>
+      <c r="G3" s="120" t="s">
         <v>44</v>
       </c>
-      <c r="H3" s="116" t="s">
+      <c r="H3" s="119" t="s">
         <v>6</v>
       </c>
-      <c r="I3" s="123" t="s">
+      <c r="I3" s="126" t="s">
         <v>78</v>
       </c>
-      <c r="J3" s="122" t="s">
+      <c r="J3" s="125" t="s">
         <v>53</v>
       </c>
       <c r="L3" s="17"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="121"/>
-      <c r="B4" s="109"/>
-      <c r="C4" s="109"/>
-      <c r="D4" s="117"/>
-      <c r="E4" s="116"/>
-      <c r="F4" s="109"/>
-      <c r="G4" s="117"/>
-      <c r="H4" s="116"/>
-      <c r="I4" s="123"/>
-      <c r="J4" s="122"/>
+      <c r="A4" s="124"/>
+      <c r="B4" s="112"/>
+      <c r="C4" s="112"/>
+      <c r="D4" s="120"/>
+      <c r="E4" s="119"/>
+      <c r="F4" s="112"/>
+      <c r="G4" s="120"/>
+      <c r="H4" s="119"/>
+      <c r="I4" s="126"/>
+      <c r="J4" s="125"/>
       <c r="L4" s="17"/>
     </row>
     <row r="5" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2838,7 +2856,7 @@
         <v>0.121</v>
       </c>
       <c r="I5" s="75">
-        <f>D$1*H5</f>
+        <f t="shared" ref="I5:I12" si="0">D$1*H5</f>
         <v>0</v>
       </c>
       <c r="J5" s="97">
@@ -2864,22 +2882,22 @@
         <v>0</v>
       </c>
       <c r="F6" s="75">
-        <f t="shared" ref="F6:F12" si="0">D6-E6</f>
+        <f t="shared" ref="F6:F12" si="1">D6-E6</f>
         <v>149494.16</v>
       </c>
       <c r="G6" s="90">
-        <f t="shared" ref="G6:G12" si="1">F6*3%</f>
+        <f t="shared" ref="G6:G12" si="2">F6*3%</f>
         <v>4484.8248000000003</v>
       </c>
       <c r="H6" s="74">
         <v>0.122</v>
       </c>
       <c r="I6" s="75">
-        <f>D$1*H6</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J6" s="97">
-        <f t="shared" ref="J6:J12" si="2">+G6+I6+F6</f>
+        <f t="shared" ref="J6:J12" si="3">+G6+I6+F6</f>
         <v>153978.98480000001</v>
       </c>
       <c r="L6" s="17"/>
@@ -2902,22 +2920,22 @@
         <v>12636</v>
       </c>
       <c r="F7" s="75">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G7" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="H7" s="74">
         <v>0.11700000000000001</v>
       </c>
       <c r="I7" s="75">
-        <f>D$1*H7</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J7" s="97">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L7" s="17"/>
@@ -2939,22 +2957,22 @@
         <v>0</v>
       </c>
       <c r="F8" s="75">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>143366.72</v>
       </c>
       <c r="G8" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>4301.0015999999996</v>
       </c>
       <c r="H8" s="74">
         <v>0.11700000000000001</v>
       </c>
       <c r="I8" s="75">
-        <f>D$1*H8</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J8" s="97">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>147667.72159999999</v>
       </c>
       <c r="L8" s="17"/>
@@ -2976,22 +2994,22 @@
         <v>0</v>
       </c>
       <c r="F9" s="75">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>133806.24000000002</v>
       </c>
       <c r="G9" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>4014.1872000000003</v>
       </c>
       <c r="H9" s="74">
         <v>0.13700000000000001</v>
       </c>
       <c r="I9" s="75">
-        <f>D$1*H9</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J9" s="97">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>137820.42720000003</v>
       </c>
       <c r="L9" s="17"/>
@@ -3013,22 +3031,22 @@
         <v>0</v>
       </c>
       <c r="F10" s="75">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>128921.28</v>
       </c>
       <c r="G10" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>3867.6383999999998</v>
       </c>
       <c r="H10" s="74">
         <v>0.13200000000000001</v>
       </c>
       <c r="I10" s="75">
-        <f>D$1*H10</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J10" s="97">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>132788.9184</v>
       </c>
       <c r="L10" s="17"/>
@@ -3051,22 +3069,22 @@
         <v>13716</v>
       </c>
       <c r="F11" s="75">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G11" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="H11" s="74">
         <v>0.127</v>
       </c>
       <c r="I11" s="75">
-        <f>D$1*H11</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J11" s="97">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L11" s="17"/>
@@ -3088,22 +3106,22 @@
         <v>0</v>
       </c>
       <c r="F12" s="75">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>13716</v>
       </c>
       <c r="G12" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>411.47999999999996</v>
       </c>
       <c r="H12" s="74">
         <v>0.127</v>
       </c>
       <c r="I12" s="75">
-        <f>D$1*H12</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J12" s="97">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>14127.48</v>
       </c>
       <c r="L12" s="17"/>
@@ -3128,7 +3146,7 @@
         <v>20624.467199999999</v>
       </c>
       <c r="H13" s="70">
-        <f t="shared" ref="H13" si="3">SUM(H5:H12)</f>
+        <f t="shared" ref="H13" si="4">SUM(H5:H12)</f>
         <v>1</v>
       </c>
       <c r="I13" s="80">

--- a/DRAGO/Noviembre/EXPENSAS-Noviembre.xlsx
+++ b/DRAGO/Noviembre/EXPENSAS-Noviembre.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\DRAGO\Noviembre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E1B08CC-58D6-4A09-952F-201ED50856C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74097835-FDA0-45B6-8241-556F5E38F925}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1011,41 +1011,41 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="18" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="25" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1928,58 +1928,58 @@
       <c r="M2" s="67"/>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A3" s="113"/>
-      <c r="B3" s="111" t="s">
+      <c r="A3" s="120"/>
+      <c r="B3" s="117" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="119" t="s">
+      <c r="C3" s="114" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="120" t="s">
+      <c r="D3" s="115" t="s">
         <v>54</v>
       </c>
-      <c r="E3" s="111" t="s">
+      <c r="E3" s="117" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="117" t="s">
+      <c r="F3" s="112" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="119" t="s">
+      <c r="G3" s="114" t="s">
         <v>52</v>
       </c>
-      <c r="H3" s="117" t="s">
+      <c r="H3" s="112" t="s">
         <v>44</v>
       </c>
-      <c r="I3" s="119" t="s">
+      <c r="I3" s="114" t="s">
         <v>6</v>
       </c>
-      <c r="J3" s="121" t="s">
+      <c r="J3" s="116" t="s">
         <v>80</v>
       </c>
-      <c r="K3" s="115" t="s">
+      <c r="K3" s="110" t="s">
         <v>69</v>
       </c>
-      <c r="L3" s="115" t="s">
+      <c r="L3" s="110" t="s">
         <v>70</v>
       </c>
-      <c r="M3" s="115" t="s">
+      <c r="M3" s="110" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A4" s="114"/>
-      <c r="B4" s="112"/>
-      <c r="C4" s="119"/>
-      <c r="D4" s="120"/>
-      <c r="E4" s="112"/>
-      <c r="F4" s="118"/>
-      <c r="G4" s="119"/>
-      <c r="H4" s="118"/>
-      <c r="I4" s="119"/>
-      <c r="J4" s="121"/>
-      <c r="K4" s="116"/>
-      <c r="L4" s="116"/>
-      <c r="M4" s="116"/>
+      <c r="A4" s="121"/>
+      <c r="B4" s="118"/>
+      <c r="C4" s="114"/>
+      <c r="D4" s="115"/>
+      <c r="E4" s="118"/>
+      <c r="F4" s="113"/>
+      <c r="G4" s="114"/>
+      <c r="H4" s="113"/>
+      <c r="I4" s="114"/>
+      <c r="J4" s="116"/>
+      <c r="K4" s="111"/>
+      <c r="L4" s="111"/>
+      <c r="M4" s="111"/>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" s="68">
@@ -2217,18 +2217,18 @@
         <v>77</v>
       </c>
       <c r="E10" s="37">
-        <v>186903.52939660478</v>
+        <v>129184.55865799999</v>
       </c>
       <c r="F10" s="85">
         <v>57107.01</v>
       </c>
       <c r="G10" s="37">
         <f t="shared" si="1"/>
-        <v>129796.51939660477</v>
+        <v>72077.548657999985</v>
       </c>
       <c r="H10" s="37">
         <f t="shared" si="2"/>
-        <v>3893.8955818981431</v>
+        <v>2162.3264597399993</v>
       </c>
       <c r="I10" s="74">
         <v>0.13200000000000001</v>
@@ -2240,11 +2240,11 @@
       </c>
       <c r="L10" s="75">
         <f t="shared" si="3"/>
-        <v>203671.47821850292</v>
+        <v>144220.93835774</v>
       </c>
       <c r="M10" s="76">
         <f t="shared" si="4"/>
-        <v>211818.33734724304</v>
+        <v>149989.7758920496</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
@@ -2346,7 +2346,7 @@
       <c r="D13" s="79"/>
       <c r="E13" s="80">
         <f>SUM(E5:E12)</f>
-        <v>562422.99900660478</v>
+        <v>504704.02826799999</v>
       </c>
       <c r="F13" s="69">
         <f>SUM(F5:F12)</f>
@@ -2355,7 +2355,7 @@
       <c r="G13" s="69"/>
       <c r="H13" s="69">
         <f>SUM(H5:H12)</f>
-        <v>5412.4228453981432</v>
+        <v>3680.8537232399995</v>
       </c>
       <c r="I13" s="70">
         <f t="shared" ref="I13" si="5">SUM(I5:I12)</f>
@@ -2371,57 +2371,57 @@
       </c>
       <c r="L13" s="80">
         <f>SUM(L5:L12)</f>
-        <v>672071.38180200313</v>
+        <v>612620.84194124001</v>
       </c>
       <c r="M13" s="81">
         <f>SUM(M5:M12)</f>
-        <v>698954.23707408318</v>
+        <v>637125.67561888974</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="C15" s="110" t="s">
+      <c r="C15" s="119" t="s">
         <v>81</v>
       </c>
-      <c r="D15" s="110"/>
-      <c r="E15" s="110"/>
-      <c r="F15" s="110"/>
-      <c r="G15" s="110"/>
-      <c r="H15" s="110"/>
-      <c r="I15" s="110"/>
-      <c r="J15" s="110"/>
-      <c r="K15" s="110"/>
-      <c r="L15" s="110"/>
+      <c r="D15" s="119"/>
+      <c r="E15" s="119"/>
+      <c r="F15" s="119"/>
+      <c r="G15" s="119"/>
+      <c r="H15" s="119"/>
+      <c r="I15" s="119"/>
+      <c r="J15" s="119"/>
+      <c r="K15" s="119"/>
+      <c r="L15" s="119"/>
     </row>
     <row r="16" spans="1:17" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="40" t="s">
         <v>48</v>
       </c>
-      <c r="C16" s="110"/>
-      <c r="D16" s="110"/>
-      <c r="E16" s="110"/>
-      <c r="F16" s="110"/>
-      <c r="G16" s="110"/>
-      <c r="H16" s="110"/>
-      <c r="I16" s="110"/>
-      <c r="J16" s="110"/>
-      <c r="K16" s="110"/>
-      <c r="L16" s="110"/>
+      <c r="C16" s="119"/>
+      <c r="D16" s="119"/>
+      <c r="E16" s="119"/>
+      <c r="F16" s="119"/>
+      <c r="G16" s="119"/>
+      <c r="H16" s="119"/>
+      <c r="I16" s="119"/>
+      <c r="J16" s="119"/>
+      <c r="K16" s="119"/>
+      <c r="L16" s="119"/>
     </row>
     <row r="17" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="24" t="s">
         <v>50</v>
       </c>
       <c r="B17" s="25"/>
-      <c r="C17" s="110"/>
-      <c r="D17" s="110"/>
-      <c r="E17" s="110"/>
-      <c r="F17" s="110"/>
-      <c r="G17" s="110"/>
-      <c r="H17" s="110"/>
-      <c r="I17" s="110"/>
-      <c r="J17" s="110"/>
-      <c r="K17" s="110"/>
-      <c r="L17" s="110"/>
+      <c r="C17" s="119"/>
+      <c r="D17" s="119"/>
+      <c r="E17" s="119"/>
+      <c r="F17" s="119"/>
+      <c r="G17" s="119"/>
+      <c r="H17" s="119"/>
+      <c r="I17" s="119"/>
+      <c r="J17" s="119"/>
+      <c r="K17" s="119"/>
+      <c r="L17" s="119"/>
       <c r="M17" s="26"/>
     </row>
     <row r="18" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
@@ -2431,16 +2431,16 @@
       <c r="B18" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C18" s="110"/>
-      <c r="D18" s="110"/>
-      <c r="E18" s="110"/>
-      <c r="F18" s="110"/>
-      <c r="G18" s="110"/>
-      <c r="H18" s="110"/>
-      <c r="I18" s="110"/>
-      <c r="J18" s="110"/>
-      <c r="K18" s="110"/>
-      <c r="L18" s="110"/>
+      <c r="C18" s="119"/>
+      <c r="D18" s="119"/>
+      <c r="E18" s="119"/>
+      <c r="F18" s="119"/>
+      <c r="G18" s="119"/>
+      <c r="H18" s="119"/>
+      <c r="I18" s="119"/>
+      <c r="J18" s="119"/>
+      <c r="K18" s="119"/>
+      <c r="L18" s="119"/>
       <c r="M18" s="36" t="s">
         <v>4</v>
       </c>
@@ -2448,16 +2448,16 @@
     <row r="19" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2"/>
       <c r="B19" s="7"/>
-      <c r="C19" s="110"/>
-      <c r="D19" s="110"/>
-      <c r="E19" s="110"/>
-      <c r="F19" s="110"/>
-      <c r="G19" s="110"/>
-      <c r="H19" s="110"/>
-      <c r="I19" s="110"/>
-      <c r="J19" s="110"/>
-      <c r="K19" s="110"/>
-      <c r="L19" s="110"/>
+      <c r="C19" s="119"/>
+      <c r="D19" s="119"/>
+      <c r="E19" s="119"/>
+      <c r="F19" s="119"/>
+      <c r="G19" s="119"/>
+      <c r="H19" s="119"/>
+      <c r="I19" s="119"/>
+      <c r="J19" s="119"/>
+      <c r="K19" s="119"/>
+      <c r="L19" s="119"/>
       <c r="M19" s="32" t="s">
         <v>5</v>
       </c>
@@ -2469,16 +2469,16 @@
       <c r="B20" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="C20" s="110"/>
-      <c r="D20" s="110"/>
-      <c r="E20" s="110"/>
-      <c r="F20" s="110"/>
-      <c r="G20" s="110"/>
-      <c r="H20" s="110"/>
-      <c r="I20" s="110"/>
-      <c r="J20" s="110"/>
-      <c r="K20" s="110"/>
-      <c r="L20" s="110"/>
+      <c r="C20" s="119"/>
+      <c r="D20" s="119"/>
+      <c r="E20" s="119"/>
+      <c r="F20" s="119"/>
+      <c r="G20" s="119"/>
+      <c r="H20" s="119"/>
+      <c r="I20" s="119"/>
+      <c r="J20" s="119"/>
+      <c r="K20" s="119"/>
+      <c r="L20" s="119"/>
       <c r="M20" s="34" t="e">
         <f>+#REF!+H20+K20</f>
         <v>#REF!</v>
@@ -2491,16 +2491,16 @@
       <c r="B21" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="C21" s="110"/>
-      <c r="D21" s="110"/>
-      <c r="E21" s="110"/>
-      <c r="F21" s="110"/>
-      <c r="G21" s="110"/>
-      <c r="H21" s="110"/>
-      <c r="I21" s="110"/>
-      <c r="J21" s="110"/>
-      <c r="K21" s="110"/>
-      <c r="L21" s="110"/>
+      <c r="C21" s="119"/>
+      <c r="D21" s="119"/>
+      <c r="E21" s="119"/>
+      <c r="F21" s="119"/>
+      <c r="G21" s="119"/>
+      <c r="H21" s="119"/>
+      <c r="I21" s="119"/>
+      <c r="J21" s="119"/>
+      <c r="K21" s="119"/>
+      <c r="L21" s="119"/>
       <c r="M21" s="34" t="e">
         <f>+#REF!+H21+K21</f>
         <v>#REF!</v>
@@ -2513,16 +2513,16 @@
       <c r="B22" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="C22" s="110"/>
-      <c r="D22" s="110"/>
-      <c r="E22" s="110"/>
-      <c r="F22" s="110"/>
-      <c r="G22" s="110"/>
-      <c r="H22" s="110"/>
-      <c r="I22" s="110"/>
-      <c r="J22" s="110"/>
-      <c r="K22" s="110"/>
-      <c r="L22" s="110"/>
+      <c r="C22" s="119"/>
+      <c r="D22" s="119"/>
+      <c r="E22" s="119"/>
+      <c r="F22" s="119"/>
+      <c r="G22" s="119"/>
+      <c r="H22" s="119"/>
+      <c r="I22" s="119"/>
+      <c r="J22" s="119"/>
+      <c r="K22" s="119"/>
+      <c r="L22" s="119"/>
       <c r="M22" s="34" t="e">
         <f>+#REF!+H22+K22</f>
         <v>#REF!</v>
@@ -2535,16 +2535,16 @@
       <c r="B23" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="C23" s="110"/>
-      <c r="D23" s="110"/>
-      <c r="E23" s="110"/>
-      <c r="F23" s="110"/>
-      <c r="G23" s="110"/>
-      <c r="H23" s="110"/>
-      <c r="I23" s="110"/>
-      <c r="J23" s="110"/>
-      <c r="K23" s="110"/>
-      <c r="L23" s="110"/>
+      <c r="C23" s="119"/>
+      <c r="D23" s="119"/>
+      <c r="E23" s="119"/>
+      <c r="F23" s="119"/>
+      <c r="G23" s="119"/>
+      <c r="H23" s="119"/>
+      <c r="I23" s="119"/>
+      <c r="J23" s="119"/>
+      <c r="K23" s="119"/>
+      <c r="L23" s="119"/>
       <c r="M23" s="34" t="e">
         <f>+#REF!+H23+K23</f>
         <v>#REF!</v>
@@ -2557,16 +2557,16 @@
       <c r="B24" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="C24" s="110"/>
-      <c r="D24" s="110"/>
-      <c r="E24" s="110"/>
-      <c r="F24" s="110"/>
-      <c r="G24" s="110"/>
-      <c r="H24" s="110"/>
-      <c r="I24" s="110"/>
-      <c r="J24" s="110"/>
-      <c r="K24" s="110"/>
-      <c r="L24" s="110"/>
+      <c r="C24" s="119"/>
+      <c r="D24" s="119"/>
+      <c r="E24" s="119"/>
+      <c r="F24" s="119"/>
+      <c r="G24" s="119"/>
+      <c r="H24" s="119"/>
+      <c r="I24" s="119"/>
+      <c r="J24" s="119"/>
+      <c r="K24" s="119"/>
+      <c r="L24" s="119"/>
       <c r="M24" s="34" t="e">
         <f>+#REF!+H24+K24</f>
         <v>#REF!</v>
@@ -2579,16 +2579,16 @@
       <c r="B25" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="C25" s="110"/>
-      <c r="D25" s="110"/>
-      <c r="E25" s="110"/>
-      <c r="F25" s="110"/>
-      <c r="G25" s="110"/>
-      <c r="H25" s="110"/>
-      <c r="I25" s="110"/>
-      <c r="J25" s="110"/>
-      <c r="K25" s="110"/>
-      <c r="L25" s="110"/>
+      <c r="C25" s="119"/>
+      <c r="D25" s="119"/>
+      <c r="E25" s="119"/>
+      <c r="F25" s="119"/>
+      <c r="G25" s="119"/>
+      <c r="H25" s="119"/>
+      <c r="I25" s="119"/>
+      <c r="J25" s="119"/>
+      <c r="K25" s="119"/>
+      <c r="L25" s="119"/>
       <c r="M25" s="34" t="e">
         <f>+#REF!+H25+K25</f>
         <v>#REF!</v>
@@ -2601,16 +2601,16 @@
       <c r="B26" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="C26" s="110"/>
-      <c r="D26" s="110"/>
-      <c r="E26" s="110"/>
-      <c r="F26" s="110"/>
-      <c r="G26" s="110"/>
-      <c r="H26" s="110"/>
-      <c r="I26" s="110"/>
-      <c r="J26" s="110"/>
-      <c r="K26" s="110"/>
-      <c r="L26" s="110"/>
+      <c r="C26" s="119"/>
+      <c r="D26" s="119"/>
+      <c r="E26" s="119"/>
+      <c r="F26" s="119"/>
+      <c r="G26" s="119"/>
+      <c r="H26" s="119"/>
+      <c r="I26" s="119"/>
+      <c r="J26" s="119"/>
+      <c r="K26" s="119"/>
+      <c r="L26" s="119"/>
       <c r="M26" s="34" t="e">
         <f>+#REF!+H26+K26</f>
         <v>#REF!</v>
@@ -2623,16 +2623,16 @@
       <c r="B27" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="C27" s="110"/>
-      <c r="D27" s="110"/>
-      <c r="E27" s="110"/>
-      <c r="F27" s="110"/>
-      <c r="G27" s="110"/>
-      <c r="H27" s="110"/>
-      <c r="I27" s="110"/>
-      <c r="J27" s="110"/>
-      <c r="K27" s="110"/>
-      <c r="L27" s="110"/>
+      <c r="C27" s="119"/>
+      <c r="D27" s="119"/>
+      <c r="E27" s="119"/>
+      <c r="F27" s="119"/>
+      <c r="G27" s="119"/>
+      <c r="H27" s="119"/>
+      <c r="I27" s="119"/>
+      <c r="J27" s="119"/>
+      <c r="K27" s="119"/>
+      <c r="L27" s="119"/>
       <c r="M27" s="34" t="e">
         <f>+#REF!+H27+K27</f>
         <v>#REF!</v>
@@ -2643,74 +2643,79 @@
         <v>10</v>
       </c>
       <c r="B28" s="9"/>
-      <c r="C28" s="110"/>
-      <c r="D28" s="110"/>
-      <c r="E28" s="110"/>
-      <c r="F28" s="110"/>
-      <c r="G28" s="110"/>
-      <c r="H28" s="110"/>
-      <c r="I28" s="110"/>
-      <c r="J28" s="110"/>
-      <c r="K28" s="110"/>
-      <c r="L28" s="110"/>
+      <c r="C28" s="119"/>
+      <c r="D28" s="119"/>
+      <c r="E28" s="119"/>
+      <c r="F28" s="119"/>
+      <c r="G28" s="119"/>
+      <c r="H28" s="119"/>
+      <c r="I28" s="119"/>
+      <c r="J28" s="119"/>
+      <c r="K28" s="119"/>
+      <c r="L28" s="119"/>
       <c r="M28" s="35" t="e">
         <f>SUM(M20:M27)</f>
         <v>#REF!</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="C29" s="110"/>
-      <c r="D29" s="110"/>
-      <c r="E29" s="110"/>
-      <c r="F29" s="110"/>
-      <c r="G29" s="110"/>
-      <c r="H29" s="110"/>
-      <c r="I29" s="110"/>
-      <c r="J29" s="110"/>
-      <c r="K29" s="110"/>
-      <c r="L29" s="110"/>
+      <c r="C29" s="119"/>
+      <c r="D29" s="119"/>
+      <c r="E29" s="119"/>
+      <c r="F29" s="119"/>
+      <c r="G29" s="119"/>
+      <c r="H29" s="119"/>
+      <c r="I29" s="119"/>
+      <c r="J29" s="119"/>
+      <c r="K29" s="119"/>
+      <c r="L29" s="119"/>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="C30" s="110"/>
-      <c r="D30" s="110"/>
-      <c r="E30" s="110"/>
-      <c r="F30" s="110"/>
-      <c r="G30" s="110"/>
-      <c r="H30" s="110"/>
-      <c r="I30" s="110"/>
-      <c r="J30" s="110"/>
-      <c r="K30" s="110"/>
-      <c r="L30" s="110"/>
+      <c r="C30" s="119"/>
+      <c r="D30" s="119"/>
+      <c r="E30" s="119"/>
+      <c r="F30" s="119"/>
+      <c r="G30" s="119"/>
+      <c r="H30" s="119"/>
+      <c r="I30" s="119"/>
+      <c r="J30" s="119"/>
+      <c r="K30" s="119"/>
+      <c r="L30" s="119"/>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="C31" s="110"/>
-      <c r="D31" s="110"/>
-      <c r="E31" s="110"/>
-      <c r="F31" s="110"/>
-      <c r="G31" s="110"/>
-      <c r="H31" s="110"/>
-      <c r="I31" s="110"/>
-      <c r="J31" s="110"/>
-      <c r="K31" s="110"/>
-      <c r="L31" s="110"/>
+      <c r="C31" s="119"/>
+      <c r="D31" s="119"/>
+      <c r="E31" s="119"/>
+      <c r="F31" s="119"/>
+      <c r="G31" s="119"/>
+      <c r="H31" s="119"/>
+      <c r="I31" s="119"/>
+      <c r="J31" s="119"/>
+      <c r="K31" s="119"/>
+      <c r="L31" s="119"/>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="C32" s="110"/>
-      <c r="D32" s="110"/>
-      <c r="E32" s="110"/>
-      <c r="F32" s="110"/>
-      <c r="G32" s="110"/>
-      <c r="H32" s="110"/>
-      <c r="I32" s="110"/>
-      <c r="J32" s="110"/>
-      <c r="K32" s="110"/>
-      <c r="L32" s="110"/>
+      <c r="C32" s="119"/>
+      <c r="D32" s="119"/>
+      <c r="E32" s="119"/>
+      <c r="F32" s="119"/>
+      <c r="G32" s="119"/>
+      <c r="H32" s="119"/>
+      <c r="I32" s="119"/>
+      <c r="J32" s="119"/>
+      <c r="K32" s="119"/>
+      <c r="L32" s="119"/>
     </row>
     <row r="39" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E39" s="39"/>
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="C15:L32"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="K3:K4"/>
+    <mergeCell ref="L3:L4"/>
     <mergeCell ref="M3:M4"/>
     <mergeCell ref="H3:H4"/>
     <mergeCell ref="F3:F4"/>
@@ -2720,11 +2725,6 @@
     <mergeCell ref="J3:J4"/>
     <mergeCell ref="I3:I4"/>
     <mergeCell ref="E3:E4"/>
-    <mergeCell ref="C15:L32"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="K3:K4"/>
-    <mergeCell ref="L3:L4"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -2786,25 +2786,25 @@
       <c r="A3" s="123" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="111" t="s">
+      <c r="B3" s="117" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="111" t="s">
+      <c r="C3" s="117" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="120" t="s">
+      <c r="D3" s="115" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="119" t="s">
+      <c r="E3" s="114" t="s">
         <v>51</v>
       </c>
-      <c r="F3" s="111" t="s">
+      <c r="F3" s="117" t="s">
         <v>86</v>
       </c>
-      <c r="G3" s="120" t="s">
+      <c r="G3" s="115" t="s">
         <v>44</v>
       </c>
-      <c r="H3" s="119" t="s">
+      <c r="H3" s="114" t="s">
         <v>6</v>
       </c>
       <c r="I3" s="126" t="s">
@@ -2817,13 +2817,13 @@
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="124"/>
-      <c r="B4" s="112"/>
-      <c r="C4" s="112"/>
-      <c r="D4" s="120"/>
-      <c r="E4" s="119"/>
-      <c r="F4" s="112"/>
-      <c r="G4" s="120"/>
-      <c r="H4" s="119"/>
+      <c r="B4" s="118"/>
+      <c r="C4" s="118"/>
+      <c r="D4" s="115"/>
+      <c r="E4" s="114"/>
+      <c r="F4" s="118"/>
+      <c r="G4" s="115"/>
+      <c r="H4" s="114"/>
       <c r="I4" s="126"/>
       <c r="J4" s="125"/>
       <c r="L4" s="17"/>

--- a/DRAGO/Noviembre/EXPENSAS-Noviembre.xlsx
+++ b/DRAGO/Noviembre/EXPENSAS-Noviembre.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\DRAGO\Noviembre\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\DRAGO\Noviembre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74097835-FDA0-45B6-8241-556F5E38F925}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45D3511C-D059-4994-871C-050D8B7BD10D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="detalle y gastos" sheetId="3" r:id="rId1"/>
@@ -1011,6 +1011,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -1031,21 +1046,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="25" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1430,16 +1430,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:H57"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
-    <col min="2" max="2" width="40.28515625" customWidth="1"/>
-    <col min="3" max="3" width="16.42578125" customWidth="1"/>
-    <col min="4" max="4" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="40.33203125" customWidth="1"/>
+    <col min="3" max="3" width="16.44140625" customWidth="1"/>
+    <col min="4" max="4" width="12.109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
         <v>17</v>
       </c>
@@ -1447,22 +1447,22 @@
         <v>61</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B4" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3"/>
       <c r="B5" s="21"/>
       <c r="C5" s="3"/>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="22" t="s">
         <v>35</v>
       </c>
@@ -1473,17 +1473,17 @@
         <v>82</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="3"/>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="13" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>37</v>
       </c>
@@ -1491,7 +1491,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>38</v>
       </c>
@@ -1499,24 +1499,24 @@
         <v>46</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" s="19" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" s="53" t="s">
         <v>12</v>
       </c>
       <c r="B16" s="46"/>
       <c r="C16" s="84"/>
     </row>
-    <row r="17" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="46" t="s">
         <v>49</v>
       </c>
@@ -1529,7 +1529,7 @@
       <c r="D17" s="5"/>
       <c r="E17" s="12"/>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" s="46" t="s">
         <v>62</v>
       </c>
@@ -1540,7 +1540,7 @@
       <c r="D18" s="38"/>
       <c r="E18" s="12"/>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" s="46" t="s">
         <v>42</v>
       </c>
@@ -1555,7 +1555,7 @@
       <c r="F19" s="14"/>
       <c r="H19" s="86"/>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" s="46" t="s">
         <v>31</v>
       </c>
@@ -1567,7 +1567,7 @@
       <c r="F20" s="12"/>
       <c r="H20" s="86"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" s="46" t="s">
         <v>32</v>
       </c>
@@ -1583,7 +1583,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" s="57"/>
       <c r="B22" s="58"/>
       <c r="C22" s="42">
@@ -1591,14 +1591,14 @@
         <v>285426.57</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" s="53" t="s">
         <v>33</v>
       </c>
       <c r="B23" s="56"/>
       <c r="C23" s="84"/>
     </row>
-    <row r="24" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A24" s="46" t="s">
         <v>63</v>
       </c>
@@ -1611,7 +1611,7 @@
       </c>
       <c r="F24" s="18"/>
     </row>
-    <row r="25" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A25" s="46" t="s">
         <v>89</v>
       </c>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="F25" s="18"/>
     </row>
-    <row r="26" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A26" s="46" t="s">
         <v>90</v>
       </c>
@@ -1631,7 +1631,7 @@
       </c>
       <c r="F26" s="18"/>
     </row>
-    <row r="27" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A27" s="105" t="s">
         <v>88</v>
       </c>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="F27" s="18"/>
     </row>
-    <row r="28" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A28" s="46" t="s">
         <v>68</v>
       </c>
@@ -1651,7 +1651,7 @@
       <c r="E28" s="12"/>
       <c r="F28" s="18"/>
     </row>
-    <row r="29" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A29" s="57"/>
       <c r="B29" s="58"/>
       <c r="C29" s="42">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="F29" s="18"/>
     </row>
-    <row r="30" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A30" s="49" t="s">
         <v>67</v>
       </c>
@@ -1671,24 +1671,24 @@
       </c>
       <c r="F30" s="18"/>
     </row>
-    <row r="31" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C31" s="43"/>
       <c r="F31" s="18"/>
     </row>
-    <row r="32" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A32" s="19" t="s">
         <v>43</v>
       </c>
       <c r="C32" s="43"/>
       <c r="F32" s="18"/>
     </row>
-    <row r="33" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A33" s="108"/>
       <c r="B33" s="109"/>
       <c r="C33" s="101"/>
       <c r="F33" s="18"/>
     </row>
-    <row r="34" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A34" s="105" t="s">
         <v>85</v>
       </c>
@@ -1698,17 +1698,17 @@
       </c>
       <c r="F34" s="18"/>
     </row>
-    <row r="35" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A35" s="46"/>
       <c r="B35" s="46"/>
       <c r="C35" s="52"/>
       <c r="F35" s="18"/>
     </row>
-    <row r="36" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C36" s="44"/>
       <c r="F36" s="18"/>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" s="19" t="s">
         <v>39</v>
       </c>
@@ -1719,7 +1719,7 @@
       </c>
       <c r="E37" s="12"/>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" s="29" t="s">
         <v>14</v>
       </c>
@@ -1729,12 +1729,12 @@
         <v>710159.57000000007</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" s="5" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" s="31" t="s">
         <v>9</v>
       </c>
@@ -1745,7 +1745,7 @@
       <c r="D42" s="6"/>
       <c r="E42" s="6"/>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>8</v>
       </c>
@@ -1756,7 +1756,7 @@
       <c r="D43" s="12"/>
       <c r="E43" s="12"/>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>87</v>
       </c>
@@ -1767,7 +1767,7 @@
       <c r="D44" s="12"/>
       <c r="E44" s="12"/>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>75</v>
       </c>
@@ -1778,7 +1778,7 @@
       <c r="D45" s="12"/>
       <c r="E45" s="12"/>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>66</v>
       </c>
@@ -1787,7 +1787,7 @@
         <v>-530159.57000000007</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47" s="31" t="s">
         <v>15</v>
       </c>
@@ -1798,23 +1798,23 @@
       </c>
       <c r="D47" s="6"/>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48" s="15"/>
       <c r="B48" s="14"/>
       <c r="C48" s="16"/>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49" s="15"/>
       <c r="B49" s="14"/>
       <c r="C49" s="16"/>
       <c r="F49" s="62"/>
     </row>
-    <row r="50" spans="1:6" ht="2.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" ht="2.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="15"/>
       <c r="B50" s="14"/>
       <c r="C50" s="16"/>
     </row>
-    <row r="51" spans="1:6" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" s="45" t="s">
         <v>60</v>
       </c>
@@ -1823,12 +1823,12 @@
         <v>109834.99657000002</v>
       </c>
     </row>
-    <row r="52" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52" s="46"/>
       <c r="B52" s="46"/>
       <c r="C52" s="50"/>
     </row>
-    <row r="53" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53" s="49" t="s">
         <v>4</v>
       </c>
@@ -1838,22 +1838,22 @@
         <v>109834.99657000002</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A54" s="14"/>
       <c r="B54" s="14"/>
       <c r="C54" s="14"/>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A55" s="14"/>
       <c r="B55" s="14"/>
       <c r="C55" s="14"/>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A56" s="14"/>
       <c r="B56" s="14"/>
       <c r="C56" s="14"/>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A57" s="14"/>
       <c r="B57" s="14"/>
       <c r="C57" s="14"/>
@@ -1878,24 +1878,24 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Q39"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5.28515625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="5.33203125" style="1" customWidth="1"/>
     <col min="2" max="2" width="8" style="1" customWidth="1"/>
-    <col min="3" max="3" width="23.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.28515625" customWidth="1"/>
-    <col min="6" max="6" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.42578125" customWidth="1"/>
-    <col min="8" max="8" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.42578125" customWidth="1"/>
-    <col min="10" max="10" width="9.140625" customWidth="1"/>
-    <col min="11" max="12" width="12.42578125" customWidth="1"/>
-    <col min="13" max="13" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11.42578125" style="17"/>
+    <col min="3" max="3" width="23.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.33203125" customWidth="1"/>
+    <col min="6" max="6" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.44140625" customWidth="1"/>
+    <col min="8" max="8" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.44140625" customWidth="1"/>
+    <col min="10" max="10" width="9.109375" customWidth="1"/>
+    <col min="11" max="12" width="12.44140625" customWidth="1"/>
+    <col min="13" max="13" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.44140625" style="17"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="40" t="s">
         <v>47</v>
       </c>
@@ -1907,7 +1907,7 @@
         <v>Vto. 15/12</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2" s="71" t="str">
         <f>'detalle y gastos'!B7</f>
         <v>LIQUIDACIÓN EXPENSAS NOVIEMBRE 2025</v>
@@ -1927,61 +1927,61 @@
       <c r="L2" s="66"/>
       <c r="M2" s="67"/>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A3" s="120"/>
-      <c r="B3" s="117" t="s">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A3" s="113"/>
+      <c r="B3" s="111" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="114" t="s">
+      <c r="C3" s="119" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="115" t="s">
+      <c r="D3" s="120" t="s">
         <v>54</v>
       </c>
-      <c r="E3" s="117" t="s">
+      <c r="E3" s="111" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="112" t="s">
+      <c r="F3" s="117" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="114" t="s">
+      <c r="G3" s="119" t="s">
         <v>52</v>
       </c>
-      <c r="H3" s="112" t="s">
+      <c r="H3" s="117" t="s">
         <v>44</v>
       </c>
-      <c r="I3" s="114" t="s">
+      <c r="I3" s="119" t="s">
         <v>6</v>
       </c>
-      <c r="J3" s="116" t="s">
+      <c r="J3" s="121" t="s">
         <v>80</v>
       </c>
-      <c r="K3" s="110" t="s">
+      <c r="K3" s="115" t="s">
         <v>69</v>
       </c>
-      <c r="L3" s="110" t="s">
+      <c r="L3" s="115" t="s">
         <v>70</v>
       </c>
-      <c r="M3" s="110" t="s">
+      <c r="M3" s="115" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A4" s="121"/>
-      <c r="B4" s="118"/>
-      <c r="C4" s="114"/>
-      <c r="D4" s="115"/>
-      <c r="E4" s="118"/>
-      <c r="F4" s="113"/>
-      <c r="G4" s="114"/>
-      <c r="H4" s="113"/>
-      <c r="I4" s="114"/>
-      <c r="J4" s="116"/>
-      <c r="K4" s="111"/>
-      <c r="L4" s="111"/>
-      <c r="M4" s="111"/>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A4" s="114"/>
+      <c r="B4" s="112"/>
+      <c r="C4" s="119"/>
+      <c r="D4" s="120"/>
+      <c r="E4" s="112"/>
+      <c r="F4" s="118"/>
+      <c r="G4" s="119"/>
+      <c r="H4" s="118"/>
+      <c r="I4" s="119"/>
+      <c r="J4" s="121"/>
+      <c r="K4" s="116"/>
+      <c r="L4" s="116"/>
+      <c r="M4" s="116"/>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A5" s="68">
         <v>1</v>
       </c>
@@ -2025,7 +2025,7 @@
         <v>66710.827695200001</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A6" s="68">
         <v>2</v>
       </c>
@@ -2072,7 +2072,7 @@
       <c r="O6" s="83"/>
       <c r="Q6" s="82"/>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A7" s="68">
         <v>3</v>
       </c>
@@ -2116,7 +2116,7 @@
         <v>18842.974945600006</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A8" s="68">
         <v>4</v>
       </c>
@@ -2158,7 +2158,7 @@
         <v>118731.36329964001</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A9" s="68">
         <v>5</v>
       </c>
@@ -2203,7 +2203,7 @@
         <v>75537.135533600027</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A10" s="68">
         <v>6</v>
       </c>
@@ -2247,7 +2247,7 @@
         <v>149989.7758920496</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A11" s="68">
         <v>7</v>
       </c>
@@ -2292,7 +2292,7 @@
         <v>70023.476005600009</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A12" s="68">
         <v>8</v>
       </c>
@@ -2337,7 +2337,7 @@
         <v>70023.476005600009</v>
       </c>
     </row>
-    <row r="13" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="77" t="s">
         <v>10</v>
       </c>
@@ -2378,344 +2378,339 @@
         <v>637125.67561888974</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="C15" s="119" t="s">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="C15" s="110" t="s">
         <v>81</v>
       </c>
-      <c r="D15" s="119"/>
-      <c r="E15" s="119"/>
-      <c r="F15" s="119"/>
-      <c r="G15" s="119"/>
-      <c r="H15" s="119"/>
-      <c r="I15" s="119"/>
-      <c r="J15" s="119"/>
-      <c r="K15" s="119"/>
-      <c r="L15" s="119"/>
-    </row>
-    <row r="16" spans="1:17" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D15" s="110"/>
+      <c r="E15" s="110"/>
+      <c r="F15" s="110"/>
+      <c r="G15" s="110"/>
+      <c r="H15" s="110"/>
+      <c r="I15" s="110"/>
+      <c r="J15" s="110"/>
+      <c r="K15" s="110"/>
+      <c r="L15" s="110"/>
+    </row>
+    <row r="16" spans="1:17" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="40" t="s">
         <v>48</v>
       </c>
-      <c r="C16" s="119"/>
-      <c r="D16" s="119"/>
-      <c r="E16" s="119"/>
-      <c r="F16" s="119"/>
-      <c r="G16" s="119"/>
-      <c r="H16" s="119"/>
-      <c r="I16" s="119"/>
-      <c r="J16" s="119"/>
-      <c r="K16" s="119"/>
-      <c r="L16" s="119"/>
-    </row>
-    <row r="17" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C16" s="110"/>
+      <c r="D16" s="110"/>
+      <c r="E16" s="110"/>
+      <c r="F16" s="110"/>
+      <c r="G16" s="110"/>
+      <c r="H16" s="110"/>
+      <c r="I16" s="110"/>
+      <c r="J16" s="110"/>
+      <c r="K16" s="110"/>
+      <c r="L16" s="110"/>
+    </row>
+    <row r="17" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="24" t="s">
         <v>50</v>
       </c>
       <c r="B17" s="25"/>
-      <c r="C17" s="119"/>
-      <c r="D17" s="119"/>
-      <c r="E17" s="119"/>
-      <c r="F17" s="119"/>
-      <c r="G17" s="119"/>
-      <c r="H17" s="119"/>
-      <c r="I17" s="119"/>
-      <c r="J17" s="119"/>
-      <c r="K17" s="119"/>
-      <c r="L17" s="119"/>
+      <c r="C17" s="110"/>
+      <c r="D17" s="110"/>
+      <c r="E17" s="110"/>
+      <c r="F17" s="110"/>
+      <c r="G17" s="110"/>
+      <c r="H17" s="110"/>
+      <c r="I17" s="110"/>
+      <c r="J17" s="110"/>
+      <c r="K17" s="110"/>
+      <c r="L17" s="110"/>
       <c r="M17" s="26"/>
     </row>
-    <row r="18" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B18" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C18" s="119"/>
-      <c r="D18" s="119"/>
-      <c r="E18" s="119"/>
-      <c r="F18" s="119"/>
-      <c r="G18" s="119"/>
-      <c r="H18" s="119"/>
-      <c r="I18" s="119"/>
-      <c r="J18" s="119"/>
-      <c r="K18" s="119"/>
-      <c r="L18" s="119"/>
+      <c r="C18" s="110"/>
+      <c r="D18" s="110"/>
+      <c r="E18" s="110"/>
+      <c r="F18" s="110"/>
+      <c r="G18" s="110"/>
+      <c r="H18" s="110"/>
+      <c r="I18" s="110"/>
+      <c r="J18" s="110"/>
+      <c r="K18" s="110"/>
+      <c r="L18" s="110"/>
       <c r="M18" s="36" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="2"/>
       <c r="B19" s="7"/>
-      <c r="C19" s="119"/>
-      <c r="D19" s="119"/>
-      <c r="E19" s="119"/>
-      <c r="F19" s="119"/>
-      <c r="G19" s="119"/>
-      <c r="H19" s="119"/>
-      <c r="I19" s="119"/>
-      <c r="J19" s="119"/>
-      <c r="K19" s="119"/>
-      <c r="L19" s="119"/>
+      <c r="C19" s="110"/>
+      <c r="D19" s="110"/>
+      <c r="E19" s="110"/>
+      <c r="F19" s="110"/>
+      <c r="G19" s="110"/>
+      <c r="H19" s="110"/>
+      <c r="I19" s="110"/>
+      <c r="J19" s="110"/>
+      <c r="K19" s="110"/>
+      <c r="L19" s="110"/>
       <c r="M19" s="32" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="10">
         <v>1</v>
       </c>
       <c r="B20" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="C20" s="119"/>
-      <c r="D20" s="119"/>
-      <c r="E20" s="119"/>
-      <c r="F20" s="119"/>
-      <c r="G20" s="119"/>
-      <c r="H20" s="119"/>
-      <c r="I20" s="119"/>
-      <c r="J20" s="119"/>
-      <c r="K20" s="119"/>
-      <c r="L20" s="119"/>
+      <c r="C20" s="110"/>
+      <c r="D20" s="110"/>
+      <c r="E20" s="110"/>
+      <c r="F20" s="110"/>
+      <c r="G20" s="110"/>
+      <c r="H20" s="110"/>
+      <c r="I20" s="110"/>
+      <c r="J20" s="110"/>
+      <c r="K20" s="110"/>
+      <c r="L20" s="110"/>
       <c r="M20" s="34" t="e">
         <f>+#REF!+H20+K20</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="21" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="10">
         <v>2</v>
       </c>
       <c r="B21" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="C21" s="119"/>
-      <c r="D21" s="119"/>
-      <c r="E21" s="119"/>
-      <c r="F21" s="119"/>
-      <c r="G21" s="119"/>
-      <c r="H21" s="119"/>
-      <c r="I21" s="119"/>
-      <c r="J21" s="119"/>
-      <c r="K21" s="119"/>
-      <c r="L21" s="119"/>
+      <c r="C21" s="110"/>
+      <c r="D21" s="110"/>
+      <c r="E21" s="110"/>
+      <c r="F21" s="110"/>
+      <c r="G21" s="110"/>
+      <c r="H21" s="110"/>
+      <c r="I21" s="110"/>
+      <c r="J21" s="110"/>
+      <c r="K21" s="110"/>
+      <c r="L21" s="110"/>
       <c r="M21" s="34" t="e">
         <f>+#REF!+H21+K21</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="22" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="10">
         <v>3</v>
       </c>
       <c r="B22" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="C22" s="119"/>
-      <c r="D22" s="119"/>
-      <c r="E22" s="119"/>
-      <c r="F22" s="119"/>
-      <c r="G22" s="119"/>
-      <c r="H22" s="119"/>
-      <c r="I22" s="119"/>
-      <c r="J22" s="119"/>
-      <c r="K22" s="119"/>
-      <c r="L22" s="119"/>
+      <c r="C22" s="110"/>
+      <c r="D22" s="110"/>
+      <c r="E22" s="110"/>
+      <c r="F22" s="110"/>
+      <c r="G22" s="110"/>
+      <c r="H22" s="110"/>
+      <c r="I22" s="110"/>
+      <c r="J22" s="110"/>
+      <c r="K22" s="110"/>
+      <c r="L22" s="110"/>
       <c r="M22" s="34" t="e">
         <f>+#REF!+H22+K22</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="23" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="10">
         <v>4</v>
       </c>
       <c r="B23" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="C23" s="119"/>
-      <c r="D23" s="119"/>
-      <c r="E23" s="119"/>
-      <c r="F23" s="119"/>
-      <c r="G23" s="119"/>
-      <c r="H23" s="119"/>
-      <c r="I23" s="119"/>
-      <c r="J23" s="119"/>
-      <c r="K23" s="119"/>
-      <c r="L23" s="119"/>
+      <c r="C23" s="110"/>
+      <c r="D23" s="110"/>
+      <c r="E23" s="110"/>
+      <c r="F23" s="110"/>
+      <c r="G23" s="110"/>
+      <c r="H23" s="110"/>
+      <c r="I23" s="110"/>
+      <c r="J23" s="110"/>
+      <c r="K23" s="110"/>
+      <c r="L23" s="110"/>
       <c r="M23" s="34" t="e">
         <f>+#REF!+H23+K23</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="24" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="10">
         <v>5</v>
       </c>
       <c r="B24" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="C24" s="119"/>
-      <c r="D24" s="119"/>
-      <c r="E24" s="119"/>
-      <c r="F24" s="119"/>
-      <c r="G24" s="119"/>
-      <c r="H24" s="119"/>
-      <c r="I24" s="119"/>
-      <c r="J24" s="119"/>
-      <c r="K24" s="119"/>
-      <c r="L24" s="119"/>
+      <c r="C24" s="110"/>
+      <c r="D24" s="110"/>
+      <c r="E24" s="110"/>
+      <c r="F24" s="110"/>
+      <c r="G24" s="110"/>
+      <c r="H24" s="110"/>
+      <c r="I24" s="110"/>
+      <c r="J24" s="110"/>
+      <c r="K24" s="110"/>
+      <c r="L24" s="110"/>
       <c r="M24" s="34" t="e">
         <f>+#REF!+H24+K24</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="25" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="10">
         <v>6</v>
       </c>
       <c r="B25" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="C25" s="119"/>
-      <c r="D25" s="119"/>
-      <c r="E25" s="119"/>
-      <c r="F25" s="119"/>
-      <c r="G25" s="119"/>
-      <c r="H25" s="119"/>
-      <c r="I25" s="119"/>
-      <c r="J25" s="119"/>
-      <c r="K25" s="119"/>
-      <c r="L25" s="119"/>
+      <c r="C25" s="110"/>
+      <c r="D25" s="110"/>
+      <c r="E25" s="110"/>
+      <c r="F25" s="110"/>
+      <c r="G25" s="110"/>
+      <c r="H25" s="110"/>
+      <c r="I25" s="110"/>
+      <c r="J25" s="110"/>
+      <c r="K25" s="110"/>
+      <c r="L25" s="110"/>
       <c r="M25" s="34" t="e">
         <f>+#REF!+H25+K25</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="26" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="10">
         <v>7</v>
       </c>
       <c r="B26" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="C26" s="119"/>
-      <c r="D26" s="119"/>
-      <c r="E26" s="119"/>
-      <c r="F26" s="119"/>
-      <c r="G26" s="119"/>
-      <c r="H26" s="119"/>
-      <c r="I26" s="119"/>
-      <c r="J26" s="119"/>
-      <c r="K26" s="119"/>
-      <c r="L26" s="119"/>
+      <c r="C26" s="110"/>
+      <c r="D26" s="110"/>
+      <c r="E26" s="110"/>
+      <c r="F26" s="110"/>
+      <c r="G26" s="110"/>
+      <c r="H26" s="110"/>
+      <c r="I26" s="110"/>
+      <c r="J26" s="110"/>
+      <c r="K26" s="110"/>
+      <c r="L26" s="110"/>
       <c r="M26" s="34" t="e">
         <f>+#REF!+H26+K26</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="27" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="10">
         <v>8</v>
       </c>
       <c r="B27" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="C27" s="119"/>
-      <c r="D27" s="119"/>
-      <c r="E27" s="119"/>
-      <c r="F27" s="119"/>
-      <c r="G27" s="119"/>
-      <c r="H27" s="119"/>
-      <c r="I27" s="119"/>
-      <c r="J27" s="119"/>
-      <c r="K27" s="119"/>
-      <c r="L27" s="119"/>
+      <c r="C27" s="110"/>
+      <c r="D27" s="110"/>
+      <c r="E27" s="110"/>
+      <c r="F27" s="110"/>
+      <c r="G27" s="110"/>
+      <c r="H27" s="110"/>
+      <c r="I27" s="110"/>
+      <c r="J27" s="110"/>
+      <c r="K27" s="110"/>
+      <c r="L27" s="110"/>
       <c r="M27" s="34" t="e">
         <f>+#REF!+H27+K27</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="28" spans="1:13" ht="15.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:13" ht="15.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="8" t="s">
         <v>10</v>
       </c>
       <c r="B28" s="9"/>
-      <c r="C28" s="119"/>
-      <c r="D28" s="119"/>
-      <c r="E28" s="119"/>
-      <c r="F28" s="119"/>
-      <c r="G28" s="119"/>
-      <c r="H28" s="119"/>
-      <c r="I28" s="119"/>
-      <c r="J28" s="119"/>
-      <c r="K28" s="119"/>
-      <c r="L28" s="119"/>
+      <c r="C28" s="110"/>
+      <c r="D28" s="110"/>
+      <c r="E28" s="110"/>
+      <c r="F28" s="110"/>
+      <c r="G28" s="110"/>
+      <c r="H28" s="110"/>
+      <c r="I28" s="110"/>
+      <c r="J28" s="110"/>
+      <c r="K28" s="110"/>
+      <c r="L28" s="110"/>
       <c r="M28" s="35" t="e">
         <f>SUM(M20:M27)</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="C29" s="119"/>
-      <c r="D29" s="119"/>
-      <c r="E29" s="119"/>
-      <c r="F29" s="119"/>
-      <c r="G29" s="119"/>
-      <c r="H29" s="119"/>
-      <c r="I29" s="119"/>
-      <c r="J29" s="119"/>
-      <c r="K29" s="119"/>
-      <c r="L29" s="119"/>
-    </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="C30" s="119"/>
-      <c r="D30" s="119"/>
-      <c r="E30" s="119"/>
-      <c r="F30" s="119"/>
-      <c r="G30" s="119"/>
-      <c r="H30" s="119"/>
-      <c r="I30" s="119"/>
-      <c r="J30" s="119"/>
-      <c r="K30" s="119"/>
-      <c r="L30" s="119"/>
-    </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="C31" s="119"/>
-      <c r="D31" s="119"/>
-      <c r="E31" s="119"/>
-      <c r="F31" s="119"/>
-      <c r="G31" s="119"/>
-      <c r="H31" s="119"/>
-      <c r="I31" s="119"/>
-      <c r="J31" s="119"/>
-      <c r="K31" s="119"/>
-      <c r="L31" s="119"/>
-    </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="C32" s="119"/>
-      <c r="D32" s="119"/>
-      <c r="E32" s="119"/>
-      <c r="F32" s="119"/>
-      <c r="G32" s="119"/>
-      <c r="H32" s="119"/>
-      <c r="I32" s="119"/>
-      <c r="J32" s="119"/>
-      <c r="K32" s="119"/>
-      <c r="L32" s="119"/>
-    </row>
-    <row r="39" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="C29" s="110"/>
+      <c r="D29" s="110"/>
+      <c r="E29" s="110"/>
+      <c r="F29" s="110"/>
+      <c r="G29" s="110"/>
+      <c r="H29" s="110"/>
+      <c r="I29" s="110"/>
+      <c r="J29" s="110"/>
+      <c r="K29" s="110"/>
+      <c r="L29" s="110"/>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="C30" s="110"/>
+      <c r="D30" s="110"/>
+      <c r="E30" s="110"/>
+      <c r="F30" s="110"/>
+      <c r="G30" s="110"/>
+      <c r="H30" s="110"/>
+      <c r="I30" s="110"/>
+      <c r="J30" s="110"/>
+      <c r="K30" s="110"/>
+      <c r="L30" s="110"/>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="C31" s="110"/>
+      <c r="D31" s="110"/>
+      <c r="E31" s="110"/>
+      <c r="F31" s="110"/>
+      <c r="G31" s="110"/>
+      <c r="H31" s="110"/>
+      <c r="I31" s="110"/>
+      <c r="J31" s="110"/>
+      <c r="K31" s="110"/>
+      <c r="L31" s="110"/>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="C32" s="110"/>
+      <c r="D32" s="110"/>
+      <c r="E32" s="110"/>
+      <c r="F32" s="110"/>
+      <c r="G32" s="110"/>
+      <c r="H32" s="110"/>
+      <c r="I32" s="110"/>
+      <c r="J32" s="110"/>
+      <c r="K32" s="110"/>
+      <c r="L32" s="110"/>
+    </row>
+    <row r="39" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E39" s="39"/>
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="C15:L32"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="K3:K4"/>
-    <mergeCell ref="L3:L4"/>
     <mergeCell ref="M3:M4"/>
     <mergeCell ref="H3:H4"/>
     <mergeCell ref="F3:F4"/>
@@ -2725,6 +2720,11 @@
     <mergeCell ref="J3:J4"/>
     <mergeCell ref="I3:I4"/>
     <mergeCell ref="E3:E4"/>
+    <mergeCell ref="C15:L32"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="K3:K4"/>
+    <mergeCell ref="L3:L4"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -2735,20 +2735,20 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:L13"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.28515625" customWidth="1"/>
-    <col min="3" max="3" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.28515625" customWidth="1"/>
-    <col min="5" max="5" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.140625" customWidth="1"/>
+    <col min="1" max="1" width="6.33203125" customWidth="1"/>
+    <col min="3" max="3" width="14.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.33203125" customWidth="1"/>
+    <col min="5" max="5" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.109375" customWidth="1"/>
     <col min="7" max="7" width="18" customWidth="1"/>
-    <col min="8" max="8" width="11.140625" customWidth="1"/>
-    <col min="9" max="9" width="14.7109375" customWidth="1"/>
+    <col min="8" max="8" width="11.109375" customWidth="1"/>
+    <col min="9" max="9" width="14.6640625" customWidth="1"/>
     <col min="10" max="10" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="91" t="s">
         <v>48</v>
       </c>
@@ -2765,7 +2765,7 @@
       <c r="J1" s="94"/>
       <c r="L1" s="17"/>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="95" t="s">
         <v>79</v>
       </c>
@@ -2782,29 +2782,29 @@
       <c r="J2" s="96"/>
       <c r="L2" s="17"/>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" s="123" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="117" t="s">
+      <c r="B3" s="111" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="117" t="s">
+      <c r="C3" s="111" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="115" t="s">
+      <c r="D3" s="120" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="114" t="s">
+      <c r="E3" s="119" t="s">
         <v>51</v>
       </c>
-      <c r="F3" s="117" t="s">
+      <c r="F3" s="111" t="s">
         <v>86</v>
       </c>
-      <c r="G3" s="115" t="s">
+      <c r="G3" s="120" t="s">
         <v>44</v>
       </c>
-      <c r="H3" s="114" t="s">
+      <c r="H3" s="119" t="s">
         <v>6</v>
       </c>
       <c r="I3" s="126" t="s">
@@ -2815,20 +2815,20 @@
       </c>
       <c r="L3" s="17"/>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" s="124"/>
-      <c r="B4" s="118"/>
-      <c r="C4" s="118"/>
-      <c r="D4" s="115"/>
-      <c r="E4" s="114"/>
-      <c r="F4" s="118"/>
-      <c r="G4" s="115"/>
-      <c r="H4" s="114"/>
+      <c r="B4" s="112"/>
+      <c r="C4" s="112"/>
+      <c r="D4" s="120"/>
+      <c r="E4" s="119"/>
+      <c r="F4" s="112"/>
+      <c r="G4" s="120"/>
+      <c r="H4" s="119"/>
       <c r="I4" s="126"/>
       <c r="J4" s="125"/>
       <c r="L4" s="17"/>
     </row>
-    <row r="5" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="98">
         <v>1</v>
       </c>
@@ -2865,7 +2865,7 @@
       </c>
       <c r="L5" s="17"/>
     </row>
-    <row r="6" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="98">
         <v>2</v>
       </c>
@@ -2902,7 +2902,7 @@
       </c>
       <c r="L6" s="17"/>
     </row>
-    <row r="7" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="98">
         <v>3</v>
       </c>
@@ -2940,7 +2940,7 @@
       </c>
       <c r="L7" s="17"/>
     </row>
-    <row r="8" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="98">
         <v>4</v>
       </c>
@@ -2977,7 +2977,7 @@
       </c>
       <c r="L8" s="17"/>
     </row>
-    <row r="9" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="98">
         <v>5</v>
       </c>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="L9" s="17"/>
     </row>
-    <row r="10" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="98">
         <v>6</v>
       </c>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="L10" s="17"/>
     </row>
-    <row r="11" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="98">
         <v>7</v>
       </c>
@@ -3089,7 +3089,7 @@
       </c>
       <c r="L11" s="17"/>
     </row>
-    <row r="12" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="98">
         <v>8</v>
       </c>
@@ -3126,7 +3126,7 @@
       </c>
       <c r="L12" s="17"/>
     </row>
-    <row r="13" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="77" t="s">
         <v>10</v>
       </c>
